--- a/research/traditional_assets/database/data/bulgaria/bulgaria_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_healthcare_support_services.xlsx
@@ -1139,7 +1139,7 @@
         <v>3.68162393162393</v>
       </c>
       <c r="H2">
-        <v>0.890384615384615</v>
+        <v>0.890384615384616</v>
       </c>
       <c r="I2">
         <v>0.620230381569474</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09906760740161945</v>
+        <v>0.09900903979421781</v>
       </c>
       <c r="C2">
-        <v>293.8045901698509</v>
+        <v>291.1910183664419</v>
       </c>
       <c r="D2">
-        <v>286.2545901698509</v>
+        <v>286.4190183664419</v>
       </c>
       <c r="E2">
-        <v>-172.3</v>
+        <v>-169.522</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.778</v>
       </c>
       <c r="G2">
         <v>7.55</v>
@@ -1451,28 +1451,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1397334</v>
       </c>
       <c r="N2">
-        <v>27.95510204081632</v>
+        <v>27.81536864081632</v>
       </c>
       <c r="O2">
-        <v>2.795510204081633</v>
+        <v>2.781536864081632</v>
       </c>
       <c r="P2">
-        <v>25.15959183673469</v>
+        <v>25.03383177673469</v>
       </c>
       <c r="Q2">
-        <v>44.95959183673469</v>
+        <v>44.83383177673469</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09906760740161945</v>
+        <v>0.09955185837799779</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738457</v>
+        <v>0.8315241539681534</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>200.0602722099106</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09900903979421781</v>
+        <v>0.0989504721868162</v>
       </c>
       <c r="C3">
-        <v>291.1910183664419</v>
+        <v>288.5776355708034</v>
       </c>
       <c r="D3">
-        <v>286.4190183664419</v>
+        <v>286.5836355708034</v>
       </c>
       <c r="E3">
-        <v>-169.522</v>
+        <v>-166.744</v>
       </c>
       <c r="F3">
-        <v>2.778</v>
+        <v>5.556</v>
       </c>
       <c r="G3">
         <v>7.55</v>
@@ -1533,28 +1533,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M3">
-        <v>0.1397334</v>
+        <v>0.2794668</v>
       </c>
       <c r="N3">
-        <v>27.81536864081632</v>
+        <v>27.67563524081632</v>
       </c>
       <c r="O3">
-        <v>2.781536864081632</v>
+        <v>2.767563524081632</v>
       </c>
       <c r="P3">
-        <v>25.03383177673469</v>
+        <v>24.90807171673469</v>
       </c>
       <c r="Q3">
-        <v>44.83383177673469</v>
+        <v>44.70807171673469</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09955185837799779</v>
+        <v>0.1000459920273635</v>
       </c>
       <c r="T3">
-        <v>0.8315241539681534</v>
+        <v>0.8391682443705082</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>200.0602722099106</v>
+        <v>100.0301361049553</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0989504721868162</v>
+        <v>0.09889190457941459</v>
       </c>
       <c r="C4">
-        <v>288.5776355708034</v>
+        <v>285.9644421090152</v>
       </c>
       <c r="D4">
-        <v>286.5836355708034</v>
+        <v>286.7484421090152</v>
       </c>
       <c r="E4">
-        <v>-166.744</v>
+        <v>-163.966</v>
       </c>
       <c r="F4">
-        <v>5.556</v>
+        <v>8.334</v>
       </c>
       <c r="G4">
         <v>7.55</v>
@@ -1615,28 +1615,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M4">
-        <v>0.2794668</v>
+        <v>0.4192002</v>
       </c>
       <c r="N4">
-        <v>27.67563524081632</v>
+        <v>27.53590184081633</v>
       </c>
       <c r="O4">
-        <v>2.767563524081632</v>
+        <v>2.753590184081633</v>
       </c>
       <c r="P4">
-        <v>24.90807171673469</v>
+        <v>24.78231165673469</v>
       </c>
       <c r="Q4">
-        <v>44.70807171673469</v>
+        <v>44.58231165673469</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1000459920273635</v>
+        <v>0.1005503139993965</v>
       </c>
       <c r="T4">
-        <v>0.8391682443705082</v>
+        <v>0.8469699448842517</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>100.0301361049553</v>
+        <v>66.68675740330355</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09889190457941459</v>
+        <v>0.09883333697201298</v>
       </c>
       <c r="C5">
-        <v>285.9644421090152</v>
+        <v>283.3514383079076</v>
       </c>
       <c r="D5">
-        <v>286.7484421090152</v>
+        <v>286.9134383079076</v>
       </c>
       <c r="E5">
-        <v>-163.966</v>
+        <v>-161.188</v>
       </c>
       <c r="F5">
-        <v>8.334</v>
+        <v>11.112</v>
       </c>
       <c r="G5">
         <v>7.55</v>
@@ -1697,28 +1697,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M5">
-        <v>0.4192002</v>
+        <v>0.5589336</v>
       </c>
       <c r="N5">
-        <v>27.53590184081633</v>
+        <v>27.39616844081633</v>
       </c>
       <c r="O5">
-        <v>2.753590184081633</v>
+        <v>2.739616844081633</v>
       </c>
       <c r="P5">
-        <v>24.78231165673469</v>
+        <v>24.65655159673469</v>
       </c>
       <c r="Q5">
-        <v>44.58231165673469</v>
+        <v>44.4565515967347</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1005503139993965</v>
+        <v>0.1010651426791802</v>
       </c>
       <c r="T5">
-        <v>0.8469699448842517</v>
+        <v>0.854934180825365</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.68675740330355</v>
+        <v>50.01506805247765</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09883333697201298</v>
+        <v>0.09877476936461133</v>
       </c>
       <c r="C6">
-        <v>283.3514383079076</v>
+        <v>280.738624495064</v>
       </c>
       <c r="D6">
-        <v>286.9134383079076</v>
+        <v>287.0786244950639</v>
       </c>
       <c r="E6">
-        <v>-161.188</v>
+        <v>-158.41</v>
       </c>
       <c r="F6">
-        <v>11.112</v>
+        <v>13.89</v>
       </c>
       <c r="G6">
         <v>7.55</v>
@@ -1779,28 +1779,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M6">
-        <v>0.5589336</v>
+        <v>0.698667</v>
       </c>
       <c r="N6">
-        <v>27.39616844081633</v>
+        <v>27.25643504081632</v>
       </c>
       <c r="O6">
-        <v>2.739616844081633</v>
+        <v>2.725643504081633</v>
       </c>
       <c r="P6">
-        <v>24.65655159673469</v>
+        <v>24.53079153673469</v>
       </c>
       <c r="Q6">
-        <v>44.4565515967347</v>
+        <v>44.33079153673469</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1010651426791802</v>
+        <v>0.1015908098574856</v>
       </c>
       <c r="T6">
-        <v>0.854934180825365</v>
+        <v>0.8630660848915541</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.01506805247765</v>
+        <v>40.01205444198212</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09877476936461133</v>
+        <v>0.09871620175720973</v>
       </c>
       <c r="C7">
-        <v>280.738624495064</v>
+        <v>278.1260009988216</v>
       </c>
       <c r="D7">
-        <v>287.0786244950639</v>
+        <v>287.2440009988216</v>
       </c>
       <c r="E7">
-        <v>-158.41</v>
+        <v>-155.632</v>
       </c>
       <c r="F7">
-        <v>13.89</v>
+        <v>16.668</v>
       </c>
       <c r="G7">
         <v>7.55</v>
@@ -1861,28 +1861,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M7">
-        <v>0.698667</v>
+        <v>0.8384004</v>
       </c>
       <c r="N7">
-        <v>27.25643504081632</v>
+        <v>27.11670164081632</v>
       </c>
       <c r="O7">
-        <v>2.725643504081633</v>
+        <v>2.711670164081633</v>
       </c>
       <c r="P7">
-        <v>24.53079153673469</v>
+        <v>24.40503147673469</v>
       </c>
       <c r="Q7">
-        <v>44.33079153673469</v>
+        <v>44.20503147673469</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1015908098574856</v>
+        <v>0.1021276614438401</v>
       </c>
       <c r="T7">
-        <v>0.8630660848915541</v>
+        <v>0.8713710081931944</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.01205444198212</v>
+        <v>33.34337870165177</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09871620175720973</v>
+        <v>0.0986576341498081</v>
       </c>
       <c r="C8">
-        <v>278.1260009988216</v>
+        <v>275.5135681482759</v>
       </c>
       <c r="D8">
-        <v>287.2440009988216</v>
+        <v>287.4095681482759</v>
       </c>
       <c r="E8">
-        <v>-155.632</v>
+        <v>-152.854</v>
       </c>
       <c r="F8">
-        <v>16.668</v>
+        <v>19.446</v>
       </c>
       <c r="G8">
         <v>7.55</v>
@@ -1943,28 +1943,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M8">
-        <v>0.8384003999999999</v>
+        <v>0.9781337999999998</v>
       </c>
       <c r="N8">
-        <v>27.11670164081632</v>
+        <v>26.97696824081633</v>
       </c>
       <c r="O8">
-        <v>2.711670164081633</v>
+        <v>2.697696824081633</v>
       </c>
       <c r="P8">
-        <v>24.40503147673469</v>
+        <v>24.27927141673469</v>
       </c>
       <c r="Q8">
-        <v>44.20503147673469</v>
+        <v>44.0792714167347</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1021276614438401</v>
+        <v>0.1026760582256001</v>
       </c>
       <c r="T8">
-        <v>0.8713710081931944</v>
+        <v>0.8798545319959449</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.34337870165177</v>
+        <v>28.58003888713009</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0986576341498081</v>
+        <v>0.09859906654240649</v>
       </c>
       <c r="C9">
-        <v>275.5135681482759</v>
+        <v>272.9013262732806</v>
       </c>
       <c r="D9">
-        <v>287.4095681482759</v>
+        <v>287.5753262732806</v>
       </c>
       <c r="E9">
-        <v>-152.854</v>
+        <v>-150.076</v>
       </c>
       <c r="F9">
-        <v>19.446</v>
+        <v>22.224</v>
       </c>
       <c r="G9">
         <v>7.55</v>
@@ -2025,28 +2025,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M9">
-        <v>0.9781338000000001</v>
+        <v>1.1178672</v>
       </c>
       <c r="N9">
-        <v>26.97696824081633</v>
+        <v>26.83723484081633</v>
       </c>
       <c r="O9">
-        <v>2.697696824081633</v>
+        <v>2.683723484081633</v>
       </c>
       <c r="P9">
-        <v>24.27927141673469</v>
+        <v>24.15351135673469</v>
       </c>
       <c r="Q9">
-        <v>44.0792714167347</v>
+        <v>43.95351135673469</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1026760582256001</v>
+        <v>0.1032363766765288</v>
       </c>
       <c r="T9">
-        <v>0.8798545319959451</v>
+        <v>0.8885224802291902</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.58003888713009</v>
+        <v>25.00753402623883</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09859906654240649</v>
+        <v>0.09854049893500487</v>
       </c>
       <c r="C10">
-        <v>272.9013262732806</v>
+        <v>270.2892757044515</v>
       </c>
       <c r="D10">
-        <v>287.5753262732806</v>
+        <v>287.7412757044515</v>
       </c>
       <c r="E10">
-        <v>-150.076</v>
+        <v>-147.298</v>
       </c>
       <c r="F10">
-        <v>22.224</v>
+        <v>25.002</v>
       </c>
       <c r="G10">
         <v>7.55</v>
@@ -2107,28 +2107,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M10">
-        <v>1.1178672</v>
+        <v>1.2576006</v>
       </c>
       <c r="N10">
-        <v>26.83723484081633</v>
+        <v>26.69750144081632</v>
       </c>
       <c r="O10">
-        <v>2.683723484081633</v>
+        <v>2.669750144081632</v>
       </c>
       <c r="P10">
-        <v>24.15351135673469</v>
+        <v>24.02775129673469</v>
       </c>
       <c r="Q10">
-        <v>43.95351135673469</v>
+        <v>43.82775129673469</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1032363766765288</v>
+        <v>0.1038090098186867</v>
       </c>
       <c r="T10">
-        <v>0.8885224802291902</v>
+        <v>0.8973809328192099</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.00753402623883</v>
+        <v>22.22891913443451</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09854049893500487</v>
+        <v>0.09848193132760326</v>
       </c>
       <c r="C11">
-        <v>270.2892757044515</v>
+        <v>267.6774167731675</v>
       </c>
       <c r="D11">
-        <v>287.7412757044515</v>
+        <v>287.9074167731674</v>
       </c>
       <c r="E11">
-        <v>-147.298</v>
+        <v>-144.52</v>
       </c>
       <c r="F11">
-        <v>25.002</v>
+        <v>27.78</v>
       </c>
       <c r="G11">
         <v>7.55</v>
@@ -2189,28 +2189,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M11">
-        <v>1.2576006</v>
+        <v>1.397334</v>
       </c>
       <c r="N11">
-        <v>26.69750144081632</v>
+        <v>26.55776804081632</v>
       </c>
       <c r="O11">
-        <v>2.669750144081632</v>
+        <v>2.655776804081633</v>
       </c>
       <c r="P11">
-        <v>24.02775129673469</v>
+        <v>23.90199123673469</v>
       </c>
       <c r="Q11">
-        <v>43.82775129673469</v>
+        <v>43.70199123673469</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1038090098186867</v>
+        <v>0.1043943681417814</v>
       </c>
       <c r="T11">
-        <v>0.8973809328192099</v>
+        <v>0.9064362399112303</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.22891913443451</v>
+        <v>20.00602722099107</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09848193132760326</v>
+        <v>0.09842336372020163</v>
       </c>
       <c r="C12">
-        <v>267.6774167731675</v>
+        <v>265.0657498115733</v>
       </c>
       <c r="D12">
-        <v>287.9074167731674</v>
+        <v>288.0737498115733</v>
       </c>
       <c r="E12">
-        <v>-144.52</v>
+        <v>-141.742</v>
       </c>
       <c r="F12">
-        <v>27.78</v>
+        <v>30.558</v>
       </c>
       <c r="G12">
         <v>7.55</v>
@@ -2271,28 +2271,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M12">
-        <v>1.397334</v>
+        <v>1.5370674</v>
       </c>
       <c r="N12">
-        <v>26.55776804081632</v>
+        <v>26.41803464081632</v>
       </c>
       <c r="O12">
-        <v>2.655776804081633</v>
+        <v>2.641803464081633</v>
       </c>
       <c r="P12">
-        <v>23.90199123673469</v>
+        <v>23.77623117673469</v>
       </c>
       <c r="Q12">
-        <v>43.70199123673469</v>
+        <v>43.57623117673469</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1043943681417814</v>
+        <v>0.1049928805844962</v>
       </c>
       <c r="T12">
-        <v>0.9064362399112303</v>
+        <v>0.9156950370502622</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.00602722099106</v>
+        <v>18.18729747362824</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09842336372020163</v>
+        <v>0.09836479611280002</v>
       </c>
       <c r="C13">
-        <v>265.0657498115733</v>
+        <v>262.4542751525819</v>
       </c>
       <c r="D13">
-        <v>288.0737498115733</v>
+        <v>288.2402751525819</v>
       </c>
       <c r="E13">
-        <v>-141.742</v>
+        <v>-138.964</v>
       </c>
       <c r="F13">
-        <v>30.558</v>
+        <v>33.336</v>
       </c>
       <c r="G13">
         <v>7.55</v>
@@ -2353,28 +2353,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M13">
-        <v>1.5370674</v>
+        <v>1.6768008</v>
       </c>
       <c r="N13">
-        <v>26.41803464081632</v>
+        <v>26.27830124081633</v>
       </c>
       <c r="O13">
-        <v>2.641803464081633</v>
+        <v>2.627830124081633</v>
       </c>
       <c r="P13">
-        <v>23.77623117673469</v>
+        <v>23.65047111673469</v>
       </c>
       <c r="Q13">
-        <v>43.57623117673469</v>
+        <v>43.45047111673469</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1049928805844962</v>
+        <v>0.1056049955827273</v>
       </c>
       <c r="T13">
-        <v>0.9156950370502622</v>
+        <v>0.9251642613969996</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.18729747362824</v>
+        <v>16.67168935082589</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09836479611280002</v>
+        <v>0.0983062285053984</v>
       </c>
       <c r="C14">
-        <v>262.4542751525819</v>
+        <v>259.8429931298764</v>
       </c>
       <c r="D14">
-        <v>288.2402751525819</v>
+        <v>288.4069931298764</v>
       </c>
       <c r="E14">
-        <v>-138.964</v>
+        <v>-136.186</v>
       </c>
       <c r="F14">
-        <v>33.336</v>
+        <v>36.114</v>
       </c>
       <c r="G14">
         <v>7.55</v>
@@ -2435,28 +2435,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M14">
-        <v>1.6768008</v>
+        <v>1.8165342</v>
       </c>
       <c r="N14">
-        <v>26.27830124081633</v>
+        <v>26.13856784081633</v>
       </c>
       <c r="O14">
-        <v>2.627830124081633</v>
+        <v>2.613856784081633</v>
       </c>
       <c r="P14">
-        <v>23.65047111673469</v>
+        <v>23.52471105673469</v>
       </c>
       <c r="Q14">
-        <v>43.45047111673469</v>
+        <v>43.32471105673469</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1056049955827273</v>
+        <v>0.1062311821901131</v>
       </c>
       <c r="T14">
-        <v>0.9251642613969996</v>
+        <v>0.9348511690620526</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.67168935082589</v>
+        <v>15.38925170845466</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0983062285053984</v>
+        <v>0.09824766089799677</v>
       </c>
       <c r="C15">
-        <v>259.8429931298764</v>
+        <v>257.2319040779123</v>
       </c>
       <c r="D15">
-        <v>288.4069931298764</v>
+        <v>288.5739040779123</v>
       </c>
       <c r="E15">
-        <v>-136.186</v>
+        <v>-133.408</v>
       </c>
       <c r="F15">
-        <v>36.114</v>
+        <v>38.892</v>
       </c>
       <c r="G15">
         <v>7.55</v>
@@ -2517,28 +2517,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M15">
-        <v>1.8165342</v>
+        <v>1.9562676</v>
       </c>
       <c r="N15">
-        <v>26.13856784081633</v>
+        <v>25.99883444081632</v>
       </c>
       <c r="O15">
-        <v>2.613856784081633</v>
+        <v>2.599883444081633</v>
       </c>
       <c r="P15">
-        <v>23.52471105673469</v>
+        <v>23.39895099673469</v>
       </c>
       <c r="Q15">
-        <v>43.32471105673469</v>
+        <v>43.19895099673469</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1062311821901131</v>
+        <v>0.1068719312767404</v>
       </c>
       <c r="T15">
-        <v>0.9348511690620526</v>
+        <v>0.9447633536495487</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.38925170845466</v>
+        <v>14.29001944356504</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09824766089799677</v>
+        <v>0.09818909329059516</v>
       </c>
       <c r="C16">
-        <v>257.2319040779123</v>
+        <v>254.6210083319198</v>
       </c>
       <c r="D16">
-        <v>288.5739040779123</v>
+        <v>288.7410083319198</v>
       </c>
       <c r="E16">
-        <v>-133.408</v>
+        <v>-130.63</v>
       </c>
       <c r="F16">
-        <v>38.892</v>
+        <v>41.67000000000001</v>
       </c>
       <c r="G16">
         <v>7.55</v>
@@ -2599,28 +2599,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M16">
-        <v>1.9562676</v>
+        <v>2.096001</v>
       </c>
       <c r="N16">
-        <v>25.99883444081632</v>
+        <v>25.85910104081632</v>
       </c>
       <c r="O16">
-        <v>2.599883444081633</v>
+        <v>2.585910104081632</v>
       </c>
       <c r="P16">
-        <v>23.39895099673469</v>
+        <v>23.27319093673469</v>
       </c>
       <c r="Q16">
-        <v>43.19895099673469</v>
+        <v>43.07319093673469</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1068719312767404</v>
+        <v>0.1075277568124649</v>
       </c>
       <c r="T16">
-        <v>0.9447633536495487</v>
+        <v>0.9549087661096919</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.29001944356504</v>
+        <v>13.33735148066071</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09818909329059516</v>
+        <v>0.09834652568319353</v>
       </c>
       <c r="C17">
-        <v>254.6210083319198</v>
+        <v>251.3942628891567</v>
       </c>
       <c r="D17">
-        <v>288.7410083319198</v>
+        <v>288.2922628891567</v>
       </c>
       <c r="E17">
-        <v>-130.63</v>
+        <v>-127.852</v>
       </c>
       <c r="F17">
-        <v>41.67</v>
+        <v>44.448</v>
       </c>
       <c r="G17">
         <v>7.55</v>
@@ -2681,45 +2681,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M17">
-        <v>2.096001</v>
+        <v>2.3024064</v>
       </c>
       <c r="N17">
-        <v>25.85910104081632</v>
+        <v>25.65269564081633</v>
       </c>
       <c r="O17">
-        <v>2.585910104081632</v>
+        <v>2.565269564081633</v>
       </c>
       <c r="P17">
-        <v>23.27319093673469</v>
+        <v>23.08742607673469</v>
       </c>
       <c r="Q17">
-        <v>43.07319093673469</v>
+        <v>42.8874260767347</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1075277568124649</v>
+        <v>0.1081991972418971</v>
       </c>
       <c r="T17">
-        <v>0.9549087661096919</v>
+        <v>0.9652957360093622</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.1</v>
       </c>
       <c r="W17">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.33735148066071</v>
+        <v>12.14168881775881</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09834652568319353</v>
+        <v>0.09830145807579191</v>
       </c>
       <c r="C18">
-        <v>251.3942628891567</v>
+        <v>248.7445810825457</v>
       </c>
       <c r="D18">
-        <v>288.2922628891567</v>
+        <v>288.4205810825457</v>
       </c>
       <c r="E18">
-        <v>-127.852</v>
+        <v>-125.074</v>
       </c>
       <c r="F18">
-        <v>44.448</v>
+        <v>47.22600000000001</v>
       </c>
       <c r="G18">
         <v>7.55</v>
@@ -2763,28 +2763,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M18">
-        <v>2.3024064</v>
+        <v>2.4463068</v>
       </c>
       <c r="N18">
-        <v>25.65269564081633</v>
+        <v>25.50879524081633</v>
       </c>
       <c r="O18">
-        <v>2.565269564081633</v>
+        <v>2.550879524081633</v>
       </c>
       <c r="P18">
-        <v>23.08742607673469</v>
+        <v>22.95791571673469</v>
       </c>
       <c r="Q18">
-        <v>42.8874260767347</v>
+        <v>42.75791571673469</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1081991972418971</v>
+        <v>0.1088868169587854</v>
       </c>
       <c r="T18">
-        <v>0.9652957360093622</v>
+        <v>0.9759329943403499</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.14168881775881</v>
+        <v>11.42747182847888</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09830145807579191</v>
+        <v>0.0982563904683903</v>
       </c>
       <c r="C19">
-        <v>248.7445810825457</v>
+        <v>246.0950135550389</v>
       </c>
       <c r="D19">
-        <v>288.4205810825457</v>
+        <v>288.5490135550389</v>
       </c>
       <c r="E19">
-        <v>-125.074</v>
+        <v>-122.296</v>
       </c>
       <c r="F19">
-        <v>47.22600000000001</v>
+        <v>50.004</v>
       </c>
       <c r="G19">
         <v>7.55</v>
@@ -2845,28 +2845,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M19">
-        <v>2.4463068</v>
+        <v>2.5902072</v>
       </c>
       <c r="N19">
-        <v>25.50879524081633</v>
+        <v>25.36489484081633</v>
       </c>
       <c r="O19">
-        <v>2.550879524081633</v>
+        <v>2.536489484081633</v>
       </c>
       <c r="P19">
-        <v>22.95791571673469</v>
+        <v>22.82840535673469</v>
       </c>
       <c r="Q19">
-        <v>42.75791571673469</v>
+        <v>42.62840535673469</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1088868169587854</v>
+        <v>0.1095912078882809</v>
       </c>
       <c r="T19">
-        <v>0.9759329943403499</v>
+        <v>0.9868296979964836</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.42747182847888</v>
+        <v>10.79261228245228</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09825639046839031</v>
+        <v>0.09821132286098869</v>
       </c>
       <c r="C20">
-        <v>246.0950135550389</v>
+        <v>243.4455604593686</v>
       </c>
       <c r="D20">
-        <v>288.5490135550389</v>
+        <v>288.6775604593686</v>
       </c>
       <c r="E20">
-        <v>-122.296</v>
+        <v>-119.518</v>
       </c>
       <c r="F20">
-        <v>50.004</v>
+        <v>52.782</v>
       </c>
       <c r="G20">
         <v>7.55</v>
@@ -2927,28 +2927,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M20">
-        <v>2.5902072</v>
+        <v>2.7341076</v>
       </c>
       <c r="N20">
-        <v>25.36489484081633</v>
+        <v>25.22099444081632</v>
       </c>
       <c r="O20">
-        <v>2.536489484081633</v>
+        <v>2.522099444081633</v>
       </c>
       <c r="P20">
-        <v>22.82840535673469</v>
+        <v>22.69889499673469</v>
       </c>
       <c r="Q20">
-        <v>42.62840535673469</v>
+        <v>42.49889499673469</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1095912078882809</v>
+        <v>0.1103129911864058</v>
       </c>
       <c r="T20">
-        <v>0.9868296979964836</v>
+        <v>0.9979954560638797</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.79261228245228</v>
+        <v>10.22458005706005</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09821132286098869</v>
+        <v>0.09847225525358708</v>
       </c>
       <c r="C21">
-        <v>243.4455604593686</v>
+        <v>239.9248837472497</v>
       </c>
       <c r="D21">
-        <v>288.6775604593686</v>
+        <v>287.9348837472497</v>
       </c>
       <c r="E21">
-        <v>-119.518</v>
+        <v>-116.74</v>
       </c>
       <c r="F21">
-        <v>52.782</v>
+        <v>55.56</v>
       </c>
       <c r="G21">
         <v>7.55</v>
@@ -3009,45 +3009,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M21">
-        <v>2.7341076</v>
+        <v>2.97246</v>
       </c>
       <c r="N21">
-        <v>25.22099444081632</v>
+        <v>24.98264204081632</v>
       </c>
       <c r="O21">
-        <v>2.522099444081633</v>
+        <v>2.498264204081632</v>
       </c>
       <c r="P21">
-        <v>22.69889499673469</v>
+        <v>22.48437783673469</v>
       </c>
       <c r="Q21">
-        <v>42.49889499673469</v>
+        <v>42.28437783673469</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1103129911864058</v>
+        <v>0.1110528190669838</v>
       </c>
       <c r="T21">
-        <v>0.9979954560638797</v>
+        <v>1.009440358082961</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.22458005706005</v>
+        <v>9.404702516035986</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09847225525358708</v>
+        <v>0.09844248764618543</v>
       </c>
       <c r="C22">
-        <v>239.9248837472497</v>
+        <v>237.2314163961847</v>
       </c>
       <c r="D22">
-        <v>287.9348837472497</v>
+        <v>288.0194163961847</v>
       </c>
       <c r="E22">
-        <v>-116.74</v>
+        <v>-113.962</v>
       </c>
       <c r="F22">
-        <v>55.56</v>
+        <v>58.33800000000001</v>
       </c>
       <c r="G22">
         <v>7.55</v>
@@ -3091,28 +3091,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M22">
-        <v>2.97246</v>
+        <v>3.121083</v>
       </c>
       <c r="N22">
-        <v>24.98264204081632</v>
+        <v>24.83401904081632</v>
       </c>
       <c r="O22">
-        <v>2.498264204081632</v>
+        <v>2.483401904081632</v>
       </c>
       <c r="P22">
-        <v>22.48437783673469</v>
+        <v>22.35061713673469</v>
       </c>
       <c r="Q22">
-        <v>42.28437783673469</v>
+        <v>42.1506171367347</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1110528190669838</v>
+        <v>0.1118113767673233</v>
       </c>
       <c r="T22">
-        <v>1.009440358082961</v>
+        <v>1.021175004456956</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.404702516035986</v>
+        <v>8.95685953908189</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09844248764618543</v>
+        <v>0.09841272003878382</v>
       </c>
       <c r="C23">
-        <v>237.2314163961847</v>
+        <v>234.5379986943121</v>
       </c>
       <c r="D23">
-        <v>288.0194163961847</v>
+        <v>288.1039986943121</v>
       </c>
       <c r="E23">
-        <v>-113.962</v>
+        <v>-111.184</v>
       </c>
       <c r="F23">
-        <v>58.338</v>
+        <v>61.116</v>
       </c>
       <c r="G23">
         <v>7.55</v>
@@ -3173,28 +3173,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M23">
-        <v>3.121083</v>
+        <v>3.269706</v>
       </c>
       <c r="N23">
-        <v>24.83401904081633</v>
+        <v>24.68539604081633</v>
       </c>
       <c r="O23">
-        <v>2.483401904081633</v>
+        <v>2.468539604081633</v>
       </c>
       <c r="P23">
-        <v>22.35061713673469</v>
+        <v>22.21685643673469</v>
       </c>
       <c r="Q23">
-        <v>42.1506171367347</v>
+        <v>42.0168564367347</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1118113767673233</v>
+        <v>0.1125893846651075</v>
       </c>
       <c r="T23">
-        <v>1.021175004456956</v>
+        <v>1.033210539199514</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.95685953908189</v>
+        <v>8.549729560032715</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09841272003878382</v>
+        <v>0.09838295243138219</v>
       </c>
       <c r="C24">
-        <v>234.5379986943121</v>
+        <v>231.8446306853859</v>
       </c>
       <c r="D24">
-        <v>288.1039986943121</v>
+        <v>288.1886306853859</v>
       </c>
       <c r="E24">
-        <v>-111.184</v>
+        <v>-108.406</v>
       </c>
       <c r="F24">
-        <v>61.116</v>
+        <v>63.89400000000001</v>
       </c>
       <c r="G24">
         <v>7.55</v>
@@ -3255,28 +3255,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M24">
-        <v>3.269706</v>
+        <v>3.418329</v>
       </c>
       <c r="N24">
-        <v>24.68539604081633</v>
+        <v>24.53677304081632</v>
       </c>
       <c r="O24">
-        <v>2.468539604081633</v>
+        <v>2.453677304081633</v>
       </c>
       <c r="P24">
-        <v>22.21685643673469</v>
+        <v>22.08309573673469</v>
       </c>
       <c r="Q24">
-        <v>42.0168564367347</v>
+        <v>41.88309573673469</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1125893846651075</v>
+        <v>0.1133876005602366</v>
       </c>
       <c r="T24">
-        <v>1.033210539199514</v>
+        <v>1.045558685234087</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.549729560032715</v>
+        <v>8.178002187857377</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09838295243138219</v>
+        <v>0.09835318482398057</v>
       </c>
       <c r="C25">
-        <v>231.8446306853859</v>
+        <v>229.1513124132118</v>
       </c>
       <c r="D25">
-        <v>288.1886306853859</v>
+        <v>288.2733124132118</v>
       </c>
       <c r="E25">
-        <v>-108.406</v>
+        <v>-105.628</v>
       </c>
       <c r="F25">
-        <v>63.89400000000001</v>
+        <v>66.67200000000001</v>
       </c>
       <c r="G25">
         <v>7.55</v>
@@ -3337,28 +3337,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M25">
-        <v>3.418329</v>
+        <v>3.566952000000001</v>
       </c>
       <c r="N25">
-        <v>24.53677304081632</v>
+        <v>24.38815004081632</v>
       </c>
       <c r="O25">
-        <v>2.453677304081633</v>
+        <v>2.438815004081633</v>
       </c>
       <c r="P25">
-        <v>22.08309573673469</v>
+        <v>21.94933503673469</v>
       </c>
       <c r="Q25">
-        <v>41.88309573673469</v>
+        <v>41.74933503673469</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1133876005602366</v>
+        <v>0.1142068221368165</v>
       </c>
       <c r="T25">
-        <v>1.045558685234087</v>
+        <v>1.058231782480097</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.178002187857377</v>
+        <v>7.837252096696653</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09835318482398057</v>
+        <v>0.09850341721657896</v>
       </c>
       <c r="C26">
-        <v>229.1513124132119</v>
+        <v>225.9464446175708</v>
       </c>
       <c r="D26">
-        <v>288.2733124132118</v>
+        <v>287.8464446175708</v>
       </c>
       <c r="E26">
-        <v>-105.628</v>
+        <v>-102.85</v>
       </c>
       <c r="F26">
-        <v>66.672</v>
+        <v>69.45</v>
       </c>
       <c r="G26">
         <v>7.55</v>
@@ -3419,45 +3419,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M26">
-        <v>3.566952</v>
+        <v>3.771135</v>
       </c>
       <c r="N26">
-        <v>24.38815004081632</v>
+        <v>24.18396704081632</v>
       </c>
       <c r="O26">
-        <v>2.438815004081633</v>
+        <v>2.418396704081633</v>
       </c>
       <c r="P26">
-        <v>21.94933503673469</v>
+        <v>21.76557033673469</v>
       </c>
       <c r="Q26">
-        <v>41.74933503673469</v>
+        <v>41.56557033673469</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1142068221368165</v>
+        <v>0.1150478896221053</v>
       </c>
       <c r="T26">
-        <v>1.058231782480097</v>
+        <v>1.071242828985999</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.1</v>
       </c>
       <c r="W26">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.837252096696655</v>
+        <v>7.412914690356172</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09850341721657896</v>
+        <v>0.09848084960917736</v>
       </c>
       <c r="C27">
-        <v>225.9464446175708</v>
+        <v>223.232487131504</v>
       </c>
       <c r="D27">
-        <v>287.8464446175708</v>
+        <v>287.910487131504</v>
       </c>
       <c r="E27">
-        <v>-102.85</v>
+        <v>-100.072</v>
       </c>
       <c r="F27">
-        <v>69.45</v>
+        <v>72.22800000000001</v>
       </c>
       <c r="G27">
         <v>7.55</v>
@@ -3501,28 +3501,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M27">
-        <v>3.771135</v>
+        <v>3.921980400000001</v>
       </c>
       <c r="N27">
-        <v>24.18396704081632</v>
+        <v>24.03312164081633</v>
       </c>
       <c r="O27">
-        <v>2.418396704081633</v>
+        <v>2.403312164081633</v>
       </c>
       <c r="P27">
-        <v>21.76557033673469</v>
+        <v>21.62980947673469</v>
       </c>
       <c r="Q27">
-        <v>41.56557033673469</v>
+        <v>41.42980947673469</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1150478896221053</v>
+        <v>0.1159116886610505</v>
       </c>
       <c r="T27">
-        <v>1.071242828985999</v>
+        <v>1.084605525397467</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.412914690356172</v>
+        <v>7.127802586880934</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09848084960917736</v>
+        <v>0.09845828200177573</v>
       </c>
       <c r="C28">
-        <v>223.232487131504</v>
+        <v>220.5185581492204</v>
       </c>
       <c r="D28">
-        <v>287.910487131504</v>
+        <v>287.9745581492205</v>
       </c>
       <c r="E28">
-        <v>-100.072</v>
+        <v>-97.294</v>
       </c>
       <c r="F28">
-        <v>72.22800000000001</v>
+        <v>75.00600000000001</v>
       </c>
       <c r="G28">
         <v>7.55</v>
@@ -3583,28 +3583,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M28">
-        <v>3.921980400000001</v>
+        <v>4.072825800000001</v>
       </c>
       <c r="N28">
-        <v>24.03312164081633</v>
+        <v>23.88227624081632</v>
       </c>
       <c r="O28">
-        <v>2.403312164081633</v>
+        <v>2.388227624081633</v>
       </c>
       <c r="P28">
-        <v>21.62980947673469</v>
+        <v>21.49404861673469</v>
       </c>
       <c r="Q28">
-        <v>41.42980947673469</v>
+        <v>41.29404861673469</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1159116886610505</v>
+        <v>0.11679915342709</v>
       </c>
       <c r="T28">
-        <v>1.084605525397467</v>
+        <v>1.098334323080482</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.127802586880934</v>
+        <v>6.863809898477935</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09845828200177573</v>
+        <v>0.09843571439437411</v>
       </c>
       <c r="C29">
-        <v>220.5185581492204</v>
+        <v>217.8046576897539</v>
       </c>
       <c r="D29">
-        <v>287.9745581492205</v>
+        <v>288.0386576897538</v>
       </c>
       <c r="E29">
-        <v>-97.294</v>
+        <v>-94.51600000000001</v>
       </c>
       <c r="F29">
-        <v>75.00600000000001</v>
+        <v>77.78400000000001</v>
       </c>
       <c r="G29">
         <v>7.55</v>
@@ -3665,28 +3665,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M29">
-        <v>4.072825800000001</v>
+        <v>4.2236712</v>
       </c>
       <c r="N29">
-        <v>23.88227624081632</v>
+        <v>23.73143084081632</v>
       </c>
       <c r="O29">
-        <v>2.388227624081633</v>
+        <v>2.373143084081633</v>
       </c>
       <c r="P29">
-        <v>21.49404861673469</v>
+        <v>21.35828775673469</v>
       </c>
       <c r="Q29">
-        <v>41.29404861673469</v>
+        <v>41.15828775673469</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.11679915342709</v>
+        <v>0.1177112699921863</v>
       </c>
       <c r="T29">
-        <v>1.098334323080482</v>
+        <v>1.112444476254692</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.863809898477935</v>
+        <v>6.618673830675154</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09843571439437411</v>
+        <v>0.09841314678697248</v>
       </c>
       <c r="C30">
-        <v>217.8046576897539</v>
+        <v>215.0907857721548</v>
       </c>
       <c r="D30">
-        <v>288.0386576897538</v>
+        <v>288.1027857721548</v>
       </c>
       <c r="E30">
-        <v>-94.51600000000001</v>
+        <v>-91.738</v>
       </c>
       <c r="F30">
-        <v>77.78400000000001</v>
+        <v>80.56200000000001</v>
       </c>
       <c r="G30">
         <v>7.55</v>
@@ -3747,28 +3747,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M30">
-        <v>4.2236712</v>
+        <v>4.374516600000001</v>
       </c>
       <c r="N30">
-        <v>23.73143084081632</v>
+        <v>23.58058544081632</v>
       </c>
       <c r="O30">
-        <v>2.373143084081633</v>
+        <v>2.358058544081632</v>
       </c>
       <c r="P30">
-        <v>21.35828775673469</v>
+        <v>21.22252689673469</v>
       </c>
       <c r="Q30">
-        <v>41.15828775673469</v>
+        <v>41.02252689673469</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1177112699921863</v>
+        <v>0.1186490799816514</v>
       </c>
       <c r="T30">
-        <v>1.112444476254692</v>
+        <v>1.1269520985324</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.618673830675154</v>
+        <v>6.390443698582907</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09841314678697247</v>
+        <v>0.09839057917957086</v>
       </c>
       <c r="C31">
-        <v>215.0907857721548</v>
+        <v>212.376942415491</v>
       </c>
       <c r="D31">
-        <v>288.1027857721548</v>
+        <v>288.166942415491</v>
       </c>
       <c r="E31">
-        <v>-91.73800000000001</v>
+        <v>-88.96000000000001</v>
       </c>
       <c r="F31">
-        <v>80.562</v>
+        <v>83.34</v>
       </c>
       <c r="G31">
         <v>7.55</v>
@@ -3829,28 +3829,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M31">
-        <v>4.3745166</v>
+        <v>4.525362</v>
       </c>
       <c r="N31">
-        <v>23.58058544081632</v>
+        <v>23.42974004081632</v>
       </c>
       <c r="O31">
-        <v>2.358058544081632</v>
+        <v>2.342974004081632</v>
       </c>
       <c r="P31">
-        <v>21.22252689673469</v>
+        <v>21.08676603673469</v>
       </c>
       <c r="Q31">
-        <v>41.02252689673469</v>
+        <v>40.88676603673469</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1186490799816514</v>
+        <v>0.1196136845422441</v>
       </c>
       <c r="T31">
-        <v>1.1269520985324</v>
+        <v>1.141874224303758</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.390443698582907</v>
+        <v>6.177428908630143</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09839057917957086</v>
+        <v>0.09864701157216924</v>
       </c>
       <c r="C32">
-        <v>212.376942415491</v>
+        <v>208.8716179951067</v>
       </c>
       <c r="D32">
-        <v>288.166942415491</v>
+        <v>287.4396179951067</v>
       </c>
       <c r="E32">
-        <v>-88.96000000000001</v>
+        <v>-86.182</v>
       </c>
       <c r="F32">
-        <v>83.34</v>
+        <v>86.11800000000001</v>
       </c>
       <c r="G32">
         <v>7.55</v>
@@ -3911,45 +3911,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M32">
-        <v>4.525362</v>
+        <v>4.762325400000001</v>
       </c>
       <c r="N32">
-        <v>23.42974004081632</v>
+        <v>23.19277664081632</v>
       </c>
       <c r="O32">
-        <v>2.342974004081632</v>
+        <v>2.319277664081632</v>
       </c>
       <c r="P32">
-        <v>21.08676603673469</v>
+        <v>20.87349897673469</v>
       </c>
       <c r="Q32">
-        <v>40.88676603673469</v>
+        <v>40.67349897673469</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1196136845422441</v>
+        <v>0.1206062486553177</v>
       </c>
       <c r="T32">
-        <v>1.141874224303758</v>
+        <v>1.157228875459792</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.177428908630143</v>
+        <v>5.870052903318265</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09864701157216924</v>
+        <v>0.09863344396476761</v>
       </c>
       <c r="C33">
-        <v>208.8716179951067</v>
+        <v>206.1320080755115</v>
       </c>
       <c r="D33">
-        <v>287.4396179951067</v>
+        <v>287.4780080755115</v>
       </c>
       <c r="E33">
-        <v>-86.182</v>
+        <v>-83.40400000000001</v>
       </c>
       <c r="F33">
-        <v>86.11800000000001</v>
+        <v>88.896</v>
       </c>
       <c r="G33">
         <v>7.55</v>
@@ -3993,28 +3993,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M33">
-        <v>4.762325400000001</v>
+        <v>4.9159488</v>
       </c>
       <c r="N33">
-        <v>23.19277664081632</v>
+        <v>23.03915324081633</v>
       </c>
       <c r="O33">
-        <v>2.319277664081632</v>
+        <v>2.303915324081633</v>
       </c>
       <c r="P33">
-        <v>20.87349897673469</v>
+        <v>20.73523791673469</v>
       </c>
       <c r="Q33">
-        <v>40.67349897673469</v>
+        <v>40.53523791673469</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1206062486553177</v>
+        <v>0.1216280058305406</v>
       </c>
       <c r="T33">
-        <v>1.157228875459792</v>
+        <v>1.173035134002769</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.870052903318265</v>
+        <v>5.686613750089571</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09863344396476761</v>
+        <v>0.09861987635736599</v>
       </c>
       <c r="C34">
-        <v>206.1320080755115</v>
+        <v>203.3924084119494</v>
       </c>
       <c r="D34">
-        <v>287.4780080755115</v>
+        <v>287.5164084119494</v>
       </c>
       <c r="E34">
-        <v>-83.40400000000001</v>
+        <v>-80.626</v>
       </c>
       <c r="F34">
-        <v>88.896</v>
+        <v>91.67400000000001</v>
       </c>
       <c r="G34">
         <v>7.55</v>
@@ -4075,28 +4075,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M34">
-        <v>4.9159488</v>
+        <v>5.069572200000001</v>
       </c>
       <c r="N34">
-        <v>23.03915324081633</v>
+        <v>22.88552984081633</v>
       </c>
       <c r="O34">
-        <v>2.303915324081633</v>
+        <v>2.288552984081633</v>
       </c>
       <c r="P34">
-        <v>20.73523791673469</v>
+        <v>20.59697685673469</v>
       </c>
       <c r="Q34">
-        <v>40.53523791673469</v>
+        <v>40.3969768567347</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1216280058305406</v>
+        <v>0.1226802632199493</v>
       </c>
       <c r="T34">
-        <v>1.173035134002769</v>
+        <v>1.189313221158968</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.686613750089571</v>
+        <v>5.514292121298977</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09861987635736599</v>
+        <v>0.09860630874996439</v>
       </c>
       <c r="C35">
-        <v>203.3924084119494</v>
+        <v>200.6528190085312</v>
       </c>
       <c r="D35">
-        <v>287.5164084119494</v>
+        <v>287.5548190085312</v>
       </c>
       <c r="E35">
-        <v>-80.626</v>
+        <v>-77.848</v>
       </c>
       <c r="F35">
-        <v>91.67400000000001</v>
+        <v>94.45200000000001</v>
       </c>
       <c r="G35">
         <v>7.55</v>
@@ -4157,28 +4157,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M35">
-        <v>5.069572200000001</v>
+        <v>5.223195600000001</v>
       </c>
       <c r="N35">
-        <v>22.88552984081633</v>
+        <v>22.73190644081632</v>
       </c>
       <c r="O35">
-        <v>2.288552984081633</v>
+        <v>2.273190644081633</v>
       </c>
       <c r="P35">
-        <v>20.59697685673469</v>
+        <v>20.45871579673469</v>
       </c>
       <c r="Q35">
-        <v>40.3969768567347</v>
+        <v>40.25871579673469</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1226802632199493</v>
+        <v>0.1237644071969158</v>
       </c>
       <c r="T35">
-        <v>1.189313221158968</v>
+        <v>1.206084583683538</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.514292121298977</v>
+        <v>5.35210705890783</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09860630874996439</v>
+        <v>0.09859274114256275</v>
       </c>
       <c r="C36">
-        <v>200.6528190085312</v>
+        <v>197.9132398693692</v>
       </c>
       <c r="D36">
-        <v>287.5548190085312</v>
+        <v>287.5932398693693</v>
       </c>
       <c r="E36">
-        <v>-77.848</v>
+        <v>-75.06999999999999</v>
       </c>
       <c r="F36">
-        <v>94.45200000000001</v>
+        <v>97.23000000000002</v>
       </c>
       <c r="G36">
         <v>7.55</v>
@@ -4239,28 +4239,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M36">
-        <v>5.223195600000001</v>
+        <v>5.376819000000001</v>
       </c>
       <c r="N36">
-        <v>22.73190644081632</v>
+        <v>22.57828304081632</v>
       </c>
       <c r="O36">
-        <v>2.273190644081633</v>
+        <v>2.257828304081632</v>
       </c>
       <c r="P36">
-        <v>20.45871579673469</v>
+        <v>20.32045473673469</v>
       </c>
       <c r="Q36">
-        <v>40.25871579673469</v>
+        <v>40.12045473673469</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1237644071969158</v>
+        <v>0.1248819094500966</v>
       </c>
       <c r="T36">
-        <v>1.206084583683538</v>
+        <v>1.22337198813194</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.35210705890783</v>
+        <v>5.199189714367606</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09859274114256275</v>
+        <v>0.09857917353516113</v>
       </c>
       <c r="C37">
-        <v>197.9132398693692</v>
+        <v>195.1736709985785</v>
       </c>
       <c r="D37">
-        <v>287.5932398693693</v>
+        <v>287.6316709985785</v>
       </c>
       <c r="E37">
-        <v>-75.06999999999999</v>
+        <v>-72.292</v>
       </c>
       <c r="F37">
-        <v>97.23000000000002</v>
+        <v>100.008</v>
       </c>
       <c r="G37">
         <v>7.55</v>
@@ -4321,28 +4321,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M37">
-        <v>5.376819000000001</v>
+        <v>5.530442400000001</v>
       </c>
       <c r="N37">
-        <v>22.57828304081632</v>
+        <v>22.42465964081632</v>
       </c>
       <c r="O37">
-        <v>2.257828304081632</v>
+        <v>2.242465964081632</v>
       </c>
       <c r="P37">
-        <v>20.32045473673469</v>
+        <v>20.18219367673469</v>
       </c>
       <c r="Q37">
-        <v>40.12045473673469</v>
+        <v>39.9821936767347</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1248819094500966</v>
+        <v>0.1260343336486893</v>
       </c>
       <c r="T37">
-        <v>1.22337198813194</v>
+        <v>1.241199623969355</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.199189714367606</v>
+        <v>5.054767777857395</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09857917353516116</v>
+        <v>0.09856560592775952</v>
       </c>
       <c r="C38">
-        <v>195.1736709985785</v>
+        <v>192.4341124002759</v>
       </c>
       <c r="D38">
-        <v>287.6316709985784</v>
+        <v>287.6701124002759</v>
       </c>
       <c r="E38">
-        <v>-72.29200000000002</v>
+        <v>-69.51400000000001</v>
       </c>
       <c r="F38">
-        <v>100.008</v>
+        <v>102.786</v>
       </c>
       <c r="G38">
         <v>7.55</v>
@@ -4403,28 +4403,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M38">
-        <v>5.5304424</v>
+        <v>5.6840658</v>
       </c>
       <c r="N38">
-        <v>22.42465964081632</v>
+        <v>22.27103624081633</v>
       </c>
       <c r="O38">
-        <v>2.242465964081632</v>
+        <v>2.227103624081633</v>
       </c>
       <c r="P38">
-        <v>20.18219367673469</v>
+        <v>20.04393261673469</v>
       </c>
       <c r="Q38">
-        <v>39.9821936767347</v>
+        <v>39.84393261673469</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1260343336486893</v>
+        <v>0.1272233427424754</v>
       </c>
       <c r="T38">
-        <v>1.241199623969355</v>
+        <v>1.259593216500021</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.054767777857395</v>
+        <v>4.918152432509899</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09856560592775952</v>
+        <v>0.0985520383203579</v>
       </c>
       <c r="C39">
-        <v>192.4341124002759</v>
+        <v>189.6945640785808</v>
       </c>
       <c r="D39">
-        <v>287.6701124002759</v>
+        <v>287.7085640785808</v>
       </c>
       <c r="E39">
-        <v>-69.51400000000001</v>
+        <v>-66.736</v>
       </c>
       <c r="F39">
-        <v>102.786</v>
+        <v>105.564</v>
       </c>
       <c r="G39">
         <v>7.55</v>
@@ -4485,28 +4485,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M39">
-        <v>5.6840658</v>
+        <v>5.837689200000001</v>
       </c>
       <c r="N39">
-        <v>22.27103624081633</v>
+        <v>22.11741284081632</v>
       </c>
       <c r="O39">
-        <v>2.227103624081633</v>
+        <v>2.211741284081632</v>
       </c>
       <c r="P39">
-        <v>20.04393261673469</v>
+        <v>19.90567155673469</v>
       </c>
       <c r="Q39">
-        <v>39.84393261673469</v>
+        <v>39.70567155673469</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1272233427424754</v>
+        <v>0.1284507069683192</v>
       </c>
       <c r="T39">
-        <v>1.259593216500021</v>
+        <v>1.278580150725225</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.918152432509899</v>
+        <v>4.78872736849648</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0985520383203579</v>
+        <v>0.09853847071295628</v>
       </c>
       <c r="C40">
-        <v>189.6945640785808</v>
+        <v>186.9550260376146</v>
       </c>
       <c r="D40">
-        <v>287.7085640785808</v>
+        <v>287.7470260376146</v>
       </c>
       <c r="E40">
-        <v>-66.736</v>
+        <v>-63.958</v>
       </c>
       <c r="F40">
-        <v>105.564</v>
+        <v>108.342</v>
       </c>
       <c r="G40">
         <v>7.55</v>
@@ -4567,28 +4567,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M40">
-        <v>5.837689200000001</v>
+        <v>5.991312600000001</v>
       </c>
       <c r="N40">
-        <v>22.11741284081632</v>
+        <v>21.96378944081632</v>
       </c>
       <c r="O40">
-        <v>2.211741284081632</v>
+        <v>2.196378944081633</v>
       </c>
       <c r="P40">
-        <v>19.90567155673469</v>
+        <v>19.76741049673469</v>
       </c>
       <c r="Q40">
-        <v>39.70567155673469</v>
+        <v>39.56741049673469</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1284507069683192</v>
+        <v>0.1297183126441906</v>
       </c>
       <c r="T40">
-        <v>1.278580150725225</v>
+        <v>1.298189607384042</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.78872736849648</v>
+        <v>4.665939487252981</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09853847071295628</v>
+        <v>0.09852490310555467</v>
       </c>
       <c r="C41">
-        <v>186.9550260376146</v>
+        <v>184.2154982815009</v>
       </c>
       <c r="D41">
-        <v>287.7470260376146</v>
+        <v>287.7854982815009</v>
       </c>
       <c r="E41">
-        <v>-63.958</v>
+        <v>-61.18000000000001</v>
       </c>
       <c r="F41">
-        <v>108.342</v>
+        <v>111.12</v>
       </c>
       <c r="G41">
         <v>7.55</v>
@@ -4649,28 +4649,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M41">
-        <v>5.991312600000001</v>
+        <v>6.144936</v>
       </c>
       <c r="N41">
-        <v>21.96378944081632</v>
+        <v>21.81016604081632</v>
       </c>
       <c r="O41">
-        <v>2.196378944081633</v>
+        <v>2.181016604081632</v>
       </c>
       <c r="P41">
-        <v>19.76741049673469</v>
+        <v>19.62914943673469</v>
       </c>
       <c r="Q41">
-        <v>39.56741049673469</v>
+        <v>39.42914943673469</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1297183126441906</v>
+        <v>0.1310281718425911</v>
       </c>
       <c r="T41">
-        <v>1.298189607384042</v>
+        <v>1.318452712598153</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.665939487252981</v>
+        <v>4.549291000071657</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09852490310555467</v>
+        <v>0.09943383549815304</v>
       </c>
       <c r="C42">
-        <v>184.2154982815009</v>
+        <v>178.8826729536854</v>
       </c>
       <c r="D42">
-        <v>287.7854982815009</v>
+        <v>285.2306729536854</v>
       </c>
       <c r="E42">
-        <v>-61.18000000000001</v>
+        <v>-58.402</v>
       </c>
       <c r="F42">
-        <v>111.12</v>
+        <v>113.898</v>
       </c>
       <c r="G42">
         <v>7.55</v>
@@ -4731,45 +4731,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M42">
-        <v>6.144936</v>
+        <v>6.583304400000001</v>
       </c>
       <c r="N42">
-        <v>21.81016604081632</v>
+        <v>21.37179764081633</v>
       </c>
       <c r="O42">
-        <v>2.181016604081632</v>
+        <v>2.137179764081633</v>
       </c>
       <c r="P42">
-        <v>19.62914943673469</v>
+        <v>19.23461787673469</v>
       </c>
       <c r="Q42">
-        <v>39.42914943673469</v>
+        <v>39.03461787673469</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1310281718425911</v>
+        <v>0.132382433047717</v>
       </c>
       <c r="T42">
-        <v>1.318452712598153</v>
+        <v>1.339402702734776</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.1</v>
       </c>
       <c r="W42">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.549291000071657</v>
+        <v>4.246363276292726</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09943383549815304</v>
+        <v>0.09944276789075143</v>
       </c>
       <c r="C43">
-        <v>178.8826729536854</v>
+        <v>176.0797908630107</v>
       </c>
       <c r="D43">
-        <v>285.2306729536854</v>
+        <v>285.2057908630107</v>
       </c>
       <c r="E43">
-        <v>-58.402</v>
+        <v>-55.624</v>
       </c>
       <c r="F43">
-        <v>113.898</v>
+        <v>116.676</v>
       </c>
       <c r="G43">
         <v>7.55</v>
@@ -4813,28 +4813,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M43">
-        <v>6.583304400000001</v>
+        <v>6.743872800000001</v>
       </c>
       <c r="N43">
-        <v>21.37179764081633</v>
+        <v>21.21122924081632</v>
       </c>
       <c r="O43">
-        <v>2.137179764081633</v>
+        <v>2.121122924081632</v>
       </c>
       <c r="P43">
-        <v>19.23461787673469</v>
+        <v>19.09010631673469</v>
       </c>
       <c r="Q43">
-        <v>39.03461787673469</v>
+        <v>38.89010631673469</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.132382433047717</v>
+        <v>0.1337833929150887</v>
       </c>
       <c r="T43">
-        <v>1.339402702734776</v>
+        <v>1.361075106324387</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.246363276292726</v>
+        <v>4.145259388761946</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09944276789075145</v>
+        <v>0.09945170028334982</v>
       </c>
       <c r="C44">
-        <v>176.0797908630107</v>
+        <v>173.2769131131344</v>
       </c>
       <c r="D44">
-        <v>285.2057908630106</v>
+        <v>285.1809131131344</v>
       </c>
       <c r="E44">
-        <v>-55.62400000000001</v>
+        <v>-52.846</v>
       </c>
       <c r="F44">
-        <v>116.676</v>
+        <v>119.454</v>
       </c>
       <c r="G44">
         <v>7.55</v>
@@ -4895,28 +4895,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M44">
-        <v>6.743872800000001</v>
+        <v>6.904441200000001</v>
       </c>
       <c r="N44">
-        <v>21.21122924081632</v>
+        <v>21.05066084081632</v>
       </c>
       <c r="O44">
-        <v>2.121122924081632</v>
+        <v>2.105066084081633</v>
       </c>
       <c r="P44">
-        <v>19.09010631673469</v>
+        <v>18.94559475673469</v>
       </c>
       <c r="Q44">
-        <v>38.89010631673469</v>
+        <v>38.74559475673469</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1337833929150887</v>
+        <v>0.1352335092690347</v>
       </c>
       <c r="T44">
-        <v>1.361075106324386</v>
+        <v>1.383507945127667</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.145259388761946</v>
+        <v>4.048858007627949</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09945170028334982</v>
+        <v>0.1008466326759482</v>
       </c>
       <c r="C45">
-        <v>173.2769131131344</v>
+        <v>166.6664094511616</v>
       </c>
       <c r="D45">
-        <v>285.1809131131344</v>
+        <v>281.3484094511616</v>
       </c>
       <c r="E45">
-        <v>-52.846</v>
+        <v>-50.06800000000001</v>
       </c>
       <c r="F45">
-        <v>119.454</v>
+        <v>122.232</v>
       </c>
       <c r="G45">
         <v>7.55</v>
@@ -4977,45 +4977,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M45">
-        <v>6.904441200000001</v>
+        <v>7.4928216</v>
       </c>
       <c r="N45">
-        <v>21.05066084081632</v>
+        <v>20.46228044081633</v>
       </c>
       <c r="O45">
-        <v>2.105066084081633</v>
+        <v>2.046228044081633</v>
       </c>
       <c r="P45">
-        <v>18.94559475673469</v>
+        <v>18.41605239673469</v>
       </c>
       <c r="Q45">
-        <v>38.74559475673469</v>
+        <v>38.2160523967347</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1352335092690347</v>
+        <v>0.1367354154927646</v>
       </c>
       <c r="T45">
-        <v>1.383507945127667</v>
+        <v>1.406741956745351</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.1</v>
       </c>
       <c r="W45">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.048858007627949</v>
+        <v>3.730917874891927</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1008466326759482</v>
+        <v>0.1008870650685466</v>
       </c>
       <c r="C46">
-        <v>166.6664094511616</v>
+        <v>163.7788591103671</v>
       </c>
       <c r="D46">
-        <v>281.3484094511616</v>
+        <v>281.2388591103671</v>
       </c>
       <c r="E46">
-        <v>-50.06800000000001</v>
+        <v>-47.29000000000001</v>
       </c>
       <c r="F46">
-        <v>122.232</v>
+        <v>125.01</v>
       </c>
       <c r="G46">
         <v>7.55</v>
@@ -5059,28 +5059,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M46">
-        <v>7.4928216</v>
+        <v>7.663113</v>
       </c>
       <c r="N46">
-        <v>20.46228044081633</v>
+        <v>20.29198904081633</v>
       </c>
       <c r="O46">
-        <v>2.046228044081633</v>
+        <v>2.029198904081633</v>
       </c>
       <c r="P46">
-        <v>18.41605239673469</v>
+        <v>18.26279013673469</v>
       </c>
       <c r="Q46">
-        <v>38.2160523967347</v>
+        <v>38.06279013673469</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1367354154927646</v>
+        <v>0.1382919364882665</v>
       </c>
       <c r="T46">
-        <v>1.406741956745351</v>
+        <v>1.430820841512769</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.730917874891927</v>
+        <v>3.648008588783217</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1008870650685466</v>
+        <v>0.100927497461145</v>
       </c>
       <c r="C47">
-        <v>163.7788591103671</v>
+        <v>160.8913940489311</v>
       </c>
       <c r="D47">
-        <v>281.2388591103671</v>
+        <v>281.1293940489311</v>
       </c>
       <c r="E47">
-        <v>-47.29000000000001</v>
+        <v>-44.512</v>
       </c>
       <c r="F47">
-        <v>125.01</v>
+        <v>127.788</v>
       </c>
       <c r="G47">
         <v>7.55</v>
@@ -5141,28 +5141,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M47">
-        <v>7.663113</v>
+        <v>7.833404400000001</v>
       </c>
       <c r="N47">
-        <v>20.29198904081633</v>
+        <v>20.12169764081632</v>
       </c>
       <c r="O47">
-        <v>2.029198904081633</v>
+        <v>2.012169764081632</v>
       </c>
       <c r="P47">
-        <v>18.26279013673469</v>
+        <v>18.10952787673469</v>
       </c>
       <c r="Q47">
-        <v>38.06279013673469</v>
+        <v>37.90952787673469</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1382919364882665</v>
+        <v>0.1399061064095277</v>
       </c>
       <c r="T47">
-        <v>1.430820841512769</v>
+        <v>1.455791536827127</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.648008588783217</v>
+        <v>3.568704054244451</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.100927497461145</v>
+        <v>0.1021523298537434</v>
       </c>
       <c r="C48">
-        <v>160.8913940489311</v>
+        <v>154.8372506598849</v>
       </c>
       <c r="D48">
-        <v>281.1293940489311</v>
+        <v>277.8532506598848</v>
       </c>
       <c r="E48">
-        <v>-44.512</v>
+        <v>-41.73400000000001</v>
       </c>
       <c r="F48">
-        <v>127.788</v>
+        <v>130.566</v>
       </c>
       <c r="G48">
         <v>7.55</v>
@@ -5223,45 +5223,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M48">
-        <v>7.833404400000001</v>
+        <v>8.369280600000002</v>
       </c>
       <c r="N48">
-        <v>20.12169764081632</v>
+        <v>19.58582144081632</v>
       </c>
       <c r="O48">
-        <v>2.012169764081632</v>
+        <v>1.958582144081633</v>
       </c>
       <c r="P48">
-        <v>18.10952787673469</v>
+        <v>17.62723929673469</v>
       </c>
       <c r="Q48">
-        <v>37.90952787673469</v>
+        <v>37.4272392967347</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1399061064095277</v>
+        <v>0.1415811884032893</v>
       </c>
       <c r="T48">
-        <v>1.455791536827127</v>
+        <v>1.481704522530708</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.1</v>
       </c>
       <c r="W48">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.568704054244451</v>
+        <v>3.340203701715572</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1021523298537434</v>
+        <v>0.1022179622463417</v>
       </c>
       <c r="C49">
-        <v>154.8372506598849</v>
+        <v>151.8858532566419</v>
       </c>
       <c r="D49">
-        <v>277.8532506598848</v>
+        <v>277.6798532566419</v>
       </c>
       <c r="E49">
-        <v>-41.73400000000001</v>
+        <v>-38.95599999999999</v>
       </c>
       <c r="F49">
-        <v>130.566</v>
+        <v>133.344</v>
       </c>
       <c r="G49">
         <v>7.55</v>
@@ -5305,28 +5305,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M49">
-        <v>8.369280600000002</v>
+        <v>8.547350400000003</v>
       </c>
       <c r="N49">
-        <v>19.58582144081632</v>
+        <v>19.40775164081632</v>
       </c>
       <c r="O49">
-        <v>1.958582144081633</v>
+        <v>1.940775164081632</v>
       </c>
       <c r="P49">
-        <v>17.62723929673469</v>
+        <v>17.46697647673469</v>
       </c>
       <c r="Q49">
-        <v>37.4272392967347</v>
+        <v>37.26697647673469</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1415811884032893</v>
+        <v>0.1433206966275802</v>
       </c>
       <c r="T49">
-        <v>1.481704522530708</v>
+        <v>1.508614161530579</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.340203701715572</v>
+        <v>3.270616124596497</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1022179622463417</v>
+        <v>0.1022835946389401</v>
       </c>
       <c r="C50">
-        <v>151.885853256642</v>
+        <v>148.934672139569</v>
       </c>
       <c r="D50">
-        <v>277.6798532566419</v>
+        <v>277.506672139569</v>
       </c>
       <c r="E50">
-        <v>-38.95600000000002</v>
+        <v>-36.178</v>
       </c>
       <c r="F50">
-        <v>133.344</v>
+        <v>136.122</v>
       </c>
       <c r="G50">
         <v>7.55</v>
@@ -5387,28 +5387,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M50">
-        <v>8.547350400000001</v>
+        <v>8.725420200000002</v>
       </c>
       <c r="N50">
-        <v>19.40775164081632</v>
+        <v>19.22968184081632</v>
       </c>
       <c r="O50">
-        <v>1.940775164081632</v>
+        <v>1.922968184081632</v>
       </c>
       <c r="P50">
-        <v>17.46697647673469</v>
+        <v>17.30671365673469</v>
       </c>
       <c r="Q50">
-        <v>37.26697647673469</v>
+        <v>37.10671365673469</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1433206966275802</v>
+        <v>0.1451284208606669</v>
       </c>
       <c r="T50">
-        <v>1.508614161530579</v>
+        <v>1.53657908049123</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.270616124596497</v>
+        <v>3.203868856747589</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1022835946389401</v>
+        <v>0.1023492270315385</v>
       </c>
       <c r="C51">
-        <v>148.934672139569</v>
+        <v>145.9837069042437</v>
       </c>
       <c r="D51">
-        <v>277.506672139569</v>
+        <v>277.3337069042437</v>
       </c>
       <c r="E51">
-        <v>-36.178</v>
+        <v>-33.40000000000001</v>
       </c>
       <c r="F51">
-        <v>136.122</v>
+        <v>138.9</v>
       </c>
       <c r="G51">
         <v>7.55</v>
@@ -5469,28 +5469,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M51">
-        <v>8.725420200000002</v>
+        <v>8.903490000000001</v>
       </c>
       <c r="N51">
-        <v>19.22968184081632</v>
+        <v>19.05161204081632</v>
       </c>
       <c r="O51">
-        <v>1.922968184081632</v>
+        <v>1.905161204081632</v>
       </c>
       <c r="P51">
-        <v>17.30671365673469</v>
+        <v>17.14645083673469</v>
       </c>
       <c r="Q51">
-        <v>37.10671365673469</v>
+        <v>36.94645083673469</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1451284208606669</v>
+        <v>0.1470084540630769</v>
       </c>
       <c r="T51">
-        <v>1.53657908049123</v>
+        <v>1.565662596210307</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.203868856747589</v>
+        <v>3.139791479612637</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1023492270315385</v>
+        <v>0.1024148594241369</v>
       </c>
       <c r="C52">
-        <v>145.9837069042437</v>
+        <v>143.032957147251</v>
       </c>
       <c r="D52">
-        <v>277.3337069042437</v>
+        <v>277.160957147251</v>
       </c>
       <c r="E52">
-        <v>-33.40000000000001</v>
+        <v>-30.62200000000001</v>
       </c>
       <c r="F52">
-        <v>138.9</v>
+        <v>141.678</v>
       </c>
       <c r="G52">
         <v>7.55</v>
@@ -5551,28 +5551,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M52">
-        <v>8.903490000000001</v>
+        <v>9.081559800000001</v>
       </c>
       <c r="N52">
-        <v>19.05161204081632</v>
+        <v>18.87354224081632</v>
       </c>
       <c r="O52">
-        <v>1.905161204081632</v>
+        <v>1.887354224081633</v>
       </c>
       <c r="P52">
-        <v>17.14645083673469</v>
+        <v>16.98618801673469</v>
       </c>
       <c r="Q52">
-        <v>36.94645083673469</v>
+        <v>36.78618801673469</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1470084540630769</v>
+        <v>0.148965223314565</v>
       </c>
       <c r="T52">
-        <v>1.565662596210307</v>
+        <v>1.595933194203632</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.139791479612637</v>
+        <v>3.078226940796704</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1024148594241369</v>
+        <v>0.1024804918167352</v>
       </c>
       <c r="C53">
-        <v>143.032957147251</v>
+        <v>140.0824224661804</v>
       </c>
       <c r="D53">
-        <v>277.160957147251</v>
+        <v>276.9884224661805</v>
       </c>
       <c r="E53">
-        <v>-30.62200000000001</v>
+        <v>-27.84399999999999</v>
       </c>
       <c r="F53">
-        <v>141.678</v>
+        <v>144.456</v>
       </c>
       <c r="G53">
         <v>7.55</v>
@@ -5633,28 +5633,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M53">
-        <v>9.081559800000001</v>
+        <v>9.259629600000002</v>
       </c>
       <c r="N53">
-        <v>18.87354224081632</v>
+        <v>18.69547244081632</v>
       </c>
       <c r="O53">
-        <v>1.887354224081633</v>
+        <v>1.869547244081633</v>
       </c>
       <c r="P53">
-        <v>16.98618801673469</v>
+        <v>16.82592519673469</v>
       </c>
       <c r="Q53">
-        <v>36.78618801673469</v>
+        <v>36.62592519673469</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.148965223314565</v>
+        <v>0.1510035246181984</v>
       </c>
       <c r="T53">
-        <v>1.595933194203632</v>
+        <v>1.627465067113345</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.078226940796704</v>
+        <v>3.019030268858305</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1024804918167352</v>
+        <v>0.1062667242093336</v>
       </c>
       <c r="C54">
-        <v>140.0824224661804</v>
+        <v>127.7021870064278</v>
       </c>
       <c r="D54">
-        <v>276.9884224661805</v>
+        <v>267.3861870064278</v>
       </c>
       <c r="E54">
-        <v>-27.84399999999999</v>
+        <v>-25.066</v>
       </c>
       <c r="F54">
-        <v>144.456</v>
+        <v>147.234</v>
       </c>
       <c r="G54">
         <v>7.55</v>
@@ -5715,45 +5715,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M54">
-        <v>9.259629600000002</v>
+        <v>10.5861246</v>
       </c>
       <c r="N54">
-        <v>18.69547244081632</v>
+        <v>17.36897744081632</v>
       </c>
       <c r="O54">
-        <v>1.869547244081633</v>
+        <v>1.736897744081632</v>
       </c>
       <c r="P54">
-        <v>16.82592519673469</v>
+        <v>15.63207969673469</v>
       </c>
       <c r="Q54">
-        <v>36.62592519673469</v>
+        <v>35.43207969673469</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1510035246181984</v>
+        <v>0.1531285621475183</v>
       </c>
       <c r="T54">
-        <v>1.627465067113345</v>
+        <v>1.660338721849004</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.1</v>
       </c>
       <c r="W54">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.019030268858305</v>
+        <v>2.640730493651692</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1062667242093336</v>
+        <v>0.106402556601932</v>
       </c>
       <c r="C55">
-        <v>127.7021870064278</v>
+        <v>124.5920586159174</v>
       </c>
       <c r="D55">
-        <v>267.3861870064278</v>
+        <v>267.0540586159174</v>
       </c>
       <c r="E55">
-        <v>-25.066</v>
+        <v>-22.28799999999998</v>
       </c>
       <c r="F55">
-        <v>147.234</v>
+        <v>150.012</v>
       </c>
       <c r="G55">
         <v>7.55</v>
@@ -5797,28 +5797,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M55">
-        <v>10.5861246</v>
+        <v>10.7858628</v>
       </c>
       <c r="N55">
-        <v>17.36897744081632</v>
+        <v>17.16923924081632</v>
       </c>
       <c r="O55">
-        <v>1.736897744081632</v>
+        <v>1.716923924081633</v>
       </c>
       <c r="P55">
-        <v>15.63207969673469</v>
+        <v>15.45231531673469</v>
       </c>
       <c r="Q55">
-        <v>35.43207969673469</v>
+        <v>35.25231531673469</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1531285621475183</v>
+        <v>0.1553459926128957</v>
       </c>
       <c r="T55">
-        <v>1.660338721849004</v>
+        <v>1.694641665920996</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.640730493651692</v>
+        <v>2.591828077102587</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.106402556601932</v>
+        <v>0.1065383889945304</v>
       </c>
       <c r="C56">
-        <v>124.5920586159174</v>
+        <v>121.4827542950462</v>
       </c>
       <c r="D56">
-        <v>267.0540586159174</v>
+        <v>266.7227542950462</v>
       </c>
       <c r="E56">
-        <v>-22.28799999999998</v>
+        <v>-19.50999999999999</v>
       </c>
       <c r="F56">
-        <v>150.012</v>
+        <v>152.79</v>
       </c>
       <c r="G56">
         <v>7.55</v>
@@ -5879,28 +5879,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M56">
-        <v>10.7858628</v>
+        <v>10.985601</v>
       </c>
       <c r="N56">
-        <v>17.16923924081632</v>
+        <v>16.96950104081632</v>
       </c>
       <c r="O56">
-        <v>1.716923924081633</v>
+        <v>1.696950104081632</v>
       </c>
       <c r="P56">
-        <v>15.45231531673469</v>
+        <v>15.27255093673469</v>
       </c>
       <c r="Q56">
-        <v>35.25231531673469</v>
+        <v>35.07255093673469</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1553459926128957</v>
+        <v>0.1576619755434009</v>
       </c>
       <c r="T56">
-        <v>1.694641665920996</v>
+        <v>1.730469185285076</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.591828077102587</v>
+        <v>2.544703930246176</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1065383889945304</v>
+        <v>0.1086398213871288</v>
       </c>
       <c r="C57">
-        <v>121.4827542950462</v>
+        <v>113.6819798225979</v>
       </c>
       <c r="D57">
-        <v>266.7227542950462</v>
+        <v>261.6999798225979</v>
       </c>
       <c r="E57">
-        <v>-19.50999999999999</v>
+        <v>-16.732</v>
       </c>
       <c r="F57">
-        <v>152.79</v>
+        <v>155.568</v>
       </c>
       <c r="G57">
         <v>7.55</v>
@@ -5961,45 +5961,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M57">
-        <v>10.985601</v>
+        <v>11.7920544</v>
       </c>
       <c r="N57">
-        <v>16.96950104081632</v>
+        <v>16.16304764081632</v>
       </c>
       <c r="O57">
-        <v>1.696950104081632</v>
+        <v>1.616304764081632</v>
       </c>
       <c r="P57">
-        <v>15.27255093673469</v>
+        <v>14.54674287673469</v>
       </c>
       <c r="Q57">
-        <v>35.07255093673469</v>
+        <v>34.34674287673469</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1576619755434009</v>
+        <v>0.1600832304252926</v>
       </c>
       <c r="T57">
-        <v>1.730469185285076</v>
+        <v>1.767925228256614</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.1</v>
       </c>
       <c r="W57">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.544703930246176</v>
+        <v>2.370672750696971</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1086398213871288</v>
+        <v>0.1088107537797271</v>
       </c>
       <c r="C58">
-        <v>113.6819798225979</v>
+        <v>110.5037296565687</v>
       </c>
       <c r="D58">
-        <v>261.6999798225979</v>
+        <v>261.2997296565687</v>
       </c>
       <c r="E58">
-        <v>-16.732</v>
+        <v>-13.95399999999998</v>
       </c>
       <c r="F58">
-        <v>155.568</v>
+        <v>158.346</v>
       </c>
       <c r="G58">
         <v>7.55</v>
@@ -6043,28 +6043,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M58">
-        <v>11.7920544</v>
+        <v>12.0026268</v>
       </c>
       <c r="N58">
-        <v>16.16304764081632</v>
+        <v>15.95247524081632</v>
       </c>
       <c r="O58">
-        <v>1.616304764081632</v>
+        <v>1.595247524081632</v>
       </c>
       <c r="P58">
-        <v>14.54674287673469</v>
+        <v>14.35722771673469</v>
       </c>
       <c r="Q58">
-        <v>34.34674287673469</v>
+        <v>34.15722771673469</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1600832304252926</v>
+        <v>0.1626171018133189</v>
       </c>
       <c r="T58">
-        <v>1.767925228256614</v>
+        <v>1.807123412761713</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.370672750696971</v>
+        <v>2.329082000684743</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1088107537797271</v>
+        <v>0.1089816861723255</v>
       </c>
       <c r="C59">
-        <v>110.5037296565687</v>
+        <v>107.3267019251431</v>
       </c>
       <c r="D59">
-        <v>261.2997296565687</v>
+        <v>260.9007019251432</v>
       </c>
       <c r="E59">
-        <v>-13.95399999999998</v>
+        <v>-11.17599999999999</v>
       </c>
       <c r="F59">
-        <v>158.346</v>
+        <v>161.124</v>
       </c>
       <c r="G59">
         <v>7.55</v>
@@ -6125,28 +6125,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M59">
-        <v>12.0026268</v>
+        <v>12.2131992</v>
       </c>
       <c r="N59">
-        <v>15.95247524081632</v>
+        <v>15.74190284081632</v>
       </c>
       <c r="O59">
-        <v>1.595247524081632</v>
+        <v>1.574190284081632</v>
       </c>
       <c r="P59">
-        <v>14.35722771673469</v>
+        <v>14.16771255673469</v>
       </c>
       <c r="Q59">
-        <v>34.15722771673469</v>
+        <v>33.96771255673469</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1626171018133189</v>
+        <v>0.1652716337436322</v>
       </c>
       <c r="T59">
-        <v>1.807123412761713</v>
+        <v>1.84818817748134</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.329082000684743</v>
+        <v>2.288925414466041</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1089816861723255</v>
+        <v>0.1091526185649239</v>
       </c>
       <c r="C60">
-        <v>107.3267019251431</v>
+        <v>104.1508910365643</v>
       </c>
       <c r="D60">
-        <v>260.9007019251431</v>
+        <v>260.5028910365643</v>
       </c>
       <c r="E60">
-        <v>-11.17600000000002</v>
+        <v>-8.398000000000025</v>
       </c>
       <c r="F60">
-        <v>161.124</v>
+        <v>163.902</v>
       </c>
       <c r="G60">
         <v>7.55</v>
@@ -6207,28 +6207,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M60">
-        <v>12.2131992</v>
+        <v>12.4237716</v>
       </c>
       <c r="N60">
-        <v>15.74190284081632</v>
+        <v>15.53133044081632</v>
       </c>
       <c r="O60">
-        <v>1.574190284081633</v>
+        <v>1.553133044081632</v>
       </c>
       <c r="P60">
-        <v>14.16771255673469</v>
+        <v>13.97819739673469</v>
       </c>
       <c r="Q60">
-        <v>33.9677125567347</v>
+        <v>33.7781973967347</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1652716337436322</v>
+        <v>0.1680556550363997</v>
       </c>
       <c r="T60">
-        <v>1.84818817748134</v>
+        <v>1.891256101455582</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.288925414466041</v>
+        <v>2.250130068458142</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1091526185649239</v>
+        <v>0.1093235509575223</v>
       </c>
       <c r="C61">
-        <v>104.1508910365643</v>
+        <v>100.9762914331272</v>
       </c>
       <c r="D61">
-        <v>260.5028910365643</v>
+        <v>260.1062914331272</v>
       </c>
       <c r="E61">
-        <v>-8.398000000000025</v>
+        <v>-5.620000000000005</v>
       </c>
       <c r="F61">
-        <v>163.902</v>
+        <v>166.68</v>
       </c>
       <c r="G61">
         <v>7.55</v>
@@ -6289,28 +6289,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M61">
-        <v>12.4237716</v>
+        <v>12.634344</v>
       </c>
       <c r="N61">
-        <v>15.53133044081632</v>
+        <v>15.32075804081632</v>
       </c>
       <c r="O61">
-        <v>1.553133044081632</v>
+        <v>1.532075804081632</v>
       </c>
       <c r="P61">
-        <v>13.97819739673469</v>
+        <v>13.78868223673469</v>
       </c>
       <c r="Q61">
-        <v>33.7781973967347</v>
+        <v>33.58868223673469</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1680556550363997</v>
+        <v>0.1709788773938057</v>
       </c>
       <c r="T61">
-        <v>1.891256101455582</v>
+        <v>1.936477421628537</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.250130068458142</v>
+        <v>2.212627900650507</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1093235509575223</v>
+        <v>0.1094944833501207</v>
       </c>
       <c r="C62">
-        <v>100.9762914331272</v>
+        <v>97.80289759092071</v>
       </c>
       <c r="D62">
-        <v>260.1062914331272</v>
+        <v>259.7108975909207</v>
       </c>
       <c r="E62">
-        <v>-5.620000000000005</v>
+        <v>-2.842000000000013</v>
       </c>
       <c r="F62">
-        <v>166.68</v>
+        <v>169.458</v>
       </c>
       <c r="G62">
         <v>7.55</v>
@@ -6371,28 +6371,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M62">
-        <v>12.634344</v>
+        <v>12.8449164</v>
       </c>
       <c r="N62">
-        <v>15.32075804081632</v>
+        <v>15.11018564081632</v>
       </c>
       <c r="O62">
-        <v>1.532075804081632</v>
+        <v>1.511018564081632</v>
       </c>
       <c r="P62">
-        <v>13.78868223673469</v>
+        <v>13.59916707673469</v>
       </c>
       <c r="Q62">
-        <v>33.58868223673469</v>
+        <v>33.39916707673469</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1709788773938057</v>
+        <v>0.174052008590053</v>
       </c>
       <c r="T62">
-        <v>1.936477421628537</v>
+        <v>1.984017783861644</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.212627900650507</v>
+        <v>2.176355312115252</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1094944833501207</v>
+        <v>0.109665415742719</v>
       </c>
       <c r="C63">
-        <v>97.80289759092071</v>
+        <v>94.63070401957074</v>
       </c>
       <c r="D63">
-        <v>259.7108975909207</v>
+        <v>259.3167040195708</v>
       </c>
       <c r="E63">
-        <v>-2.842000000000013</v>
+        <v>-0.06399999999999295</v>
       </c>
       <c r="F63">
-        <v>169.458</v>
+        <v>172.236</v>
       </c>
       <c r="G63">
         <v>7.55</v>
@@ -6453,28 +6453,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M63">
-        <v>12.8449164</v>
+        <v>13.0554888</v>
       </c>
       <c r="N63">
-        <v>15.11018564081632</v>
+        <v>14.89961324081632</v>
       </c>
       <c r="O63">
-        <v>1.511018564081632</v>
+        <v>1.489961324081632</v>
       </c>
       <c r="P63">
-        <v>13.59916707673469</v>
+        <v>13.40965191673469</v>
       </c>
       <c r="Q63">
-        <v>33.39916707673469</v>
+        <v>33.20965191673469</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.174052008590053</v>
+        <v>0.1772868835334712</v>
       </c>
       <c r="T63">
-        <v>1.984017783861644</v>
+        <v>2.034060270422809</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.176355312115252</v>
+        <v>2.141252807081135</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.109665415742719</v>
+        <v>0.1098363481353174</v>
       </c>
       <c r="C64">
-        <v>94.63070401957074</v>
+        <v>91.45970526198624</v>
       </c>
       <c r="D64">
-        <v>259.3167040195708</v>
+        <v>258.9237052619862</v>
       </c>
       <c r="E64">
-        <v>-0.06399999999999295</v>
+        <v>2.713999999999999</v>
       </c>
       <c r="F64">
-        <v>172.236</v>
+        <v>175.014</v>
       </c>
       <c r="G64">
         <v>7.55</v>
@@ -6535,28 +6535,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M64">
-        <v>13.0554888</v>
+        <v>13.2660612</v>
       </c>
       <c r="N64">
-        <v>14.89961324081632</v>
+        <v>14.68904084081632</v>
       </c>
       <c r="O64">
-        <v>1.489961324081632</v>
+        <v>1.468904084081633</v>
       </c>
       <c r="P64">
-        <v>13.40965191673469</v>
+        <v>13.22013675673469</v>
       </c>
       <c r="Q64">
-        <v>33.20965191673469</v>
+        <v>33.02013675673469</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1772868835334712</v>
+        <v>0.180696616581939</v>
       </c>
       <c r="T64">
-        <v>2.034060270422809</v>
+        <v>2.08680775625755</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.141252807081135</v>
+        <v>2.107264667286197</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1098363481353174</v>
+        <v>0.1100072805279158</v>
       </c>
       <c r="C65">
-        <v>91.45970526198624</v>
+        <v>88.28989589410739</v>
       </c>
       <c r="D65">
-        <v>258.9237052619862</v>
+        <v>258.5318958941074</v>
       </c>
       <c r="E65">
-        <v>2.713999999999999</v>
+        <v>5.49199999999999</v>
       </c>
       <c r="F65">
-        <v>175.014</v>
+        <v>177.792</v>
       </c>
       <c r="G65">
         <v>7.55</v>
@@ -6617,28 +6617,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M65">
-        <v>13.2660612</v>
+        <v>13.4766336</v>
       </c>
       <c r="N65">
-        <v>14.68904084081632</v>
+        <v>14.47846844081632</v>
       </c>
       <c r="O65">
-        <v>1.468904084081633</v>
+        <v>1.447846844081632</v>
       </c>
       <c r="P65">
-        <v>13.22013675673469</v>
+        <v>13.03062159673469</v>
       </c>
       <c r="Q65">
-        <v>33.02013675673469</v>
+        <v>32.83062159673469</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.180696616581939</v>
+        <v>0.1842957792442106</v>
       </c>
       <c r="T65">
-        <v>2.08680775625755</v>
+        <v>2.142485657971999</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.107264667286197</v>
+        <v>2.07433865685985</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1100072805279158</v>
+        <v>0.1101782129205142</v>
       </c>
       <c r="C66">
-        <v>88.28989589410739</v>
+        <v>85.12127052465578</v>
       </c>
       <c r="D66">
-        <v>258.5318958941074</v>
+        <v>258.1412705246558</v>
       </c>
       <c r="E66">
-        <v>5.49199999999999</v>
+        <v>8.27000000000001</v>
       </c>
       <c r="F66">
-        <v>177.792</v>
+        <v>180.57</v>
       </c>
       <c r="G66">
         <v>7.55</v>
@@ -6699,28 +6699,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M66">
-        <v>13.4766336</v>
+        <v>13.687206</v>
       </c>
       <c r="N66">
-        <v>14.47846844081632</v>
+        <v>14.26789604081632</v>
       </c>
       <c r="O66">
-        <v>1.447846844081632</v>
+        <v>1.426789604081632</v>
       </c>
       <c r="P66">
-        <v>13.03062159673469</v>
+        <v>12.84110643673469</v>
       </c>
       <c r="Q66">
-        <v>32.83062159673469</v>
+        <v>32.64110643673469</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1842957792442106</v>
+        <v>0.1881006083443263</v>
       </c>
       <c r="T66">
-        <v>2.142485657971999</v>
+        <v>2.201345154070131</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.07433865685985</v>
+        <v>2.042425754446621</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1101782129205142</v>
+        <v>0.1103491453131126</v>
       </c>
       <c r="C67">
-        <v>85.12127052465578</v>
+        <v>81.9538237948878</v>
       </c>
       <c r="D67">
-        <v>258.1412705246558</v>
+        <v>257.7518237948878</v>
       </c>
       <c r="E67">
-        <v>8.27000000000001</v>
+        <v>11.048</v>
       </c>
       <c r="F67">
-        <v>180.57</v>
+        <v>183.348</v>
       </c>
       <c r="G67">
         <v>7.55</v>
@@ -6781,28 +6781,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M67">
-        <v>13.687206</v>
+        <v>13.8977784</v>
       </c>
       <c r="N67">
-        <v>14.26789604081632</v>
+        <v>14.05732364081632</v>
       </c>
       <c r="O67">
-        <v>1.426789604081632</v>
+        <v>1.405732364081632</v>
       </c>
       <c r="P67">
-        <v>12.84110643673469</v>
+        <v>12.65159127673469</v>
       </c>
       <c r="Q67">
-        <v>32.64110643673469</v>
+        <v>32.45159127673469</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1881006083443263</v>
+        <v>0.1921292509209193</v>
       </c>
       <c r="T67">
-        <v>2.201345154070131</v>
+        <v>2.263666973468153</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.042425754446621</v>
+        <v>2.011479909682278</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1103491453131126</v>
+        <v>0.1190826777057109</v>
       </c>
       <c r="C68">
-        <v>81.9538237948878</v>
+        <v>60.72953807918265</v>
       </c>
       <c r="D68">
-        <v>257.7518237948878</v>
+        <v>239.3055380791826</v>
       </c>
       <c r="E68">
-        <v>11.048</v>
+        <v>13.82599999999999</v>
       </c>
       <c r="F68">
-        <v>183.348</v>
+        <v>186.126</v>
       </c>
       <c r="G68">
         <v>7.55</v>
@@ -6863,45 +6863,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M68">
-        <v>13.8977784</v>
+        <v>16.75134</v>
       </c>
       <c r="N68">
-        <v>14.05732364081632</v>
+        <v>11.20376204081633</v>
       </c>
       <c r="O68">
-        <v>1.405732364081632</v>
+        <v>1.120376204081633</v>
       </c>
       <c r="P68">
-        <v>12.65159127673469</v>
+        <v>10.08338583673469</v>
       </c>
       <c r="Q68">
-        <v>32.45159127673469</v>
+        <v>29.8833858367347</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1921292509209193</v>
+        <v>0.1964020536536695</v>
       </c>
       <c r="T68">
-        <v>2.263666973468153</v>
+        <v>2.329765872829691</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.1</v>
       </c>
       <c r="W68">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.011479909682278</v>
+        <v>1.66882780964486</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1190826777057109</v>
+        <v>0.1193814100983093</v>
       </c>
       <c r="C69">
-        <v>60.72953807918265</v>
+        <v>57.36716460993182</v>
       </c>
       <c r="D69">
-        <v>239.3055380791826</v>
+        <v>238.7211646099318</v>
       </c>
       <c r="E69">
-        <v>13.82599999999999</v>
+        <v>16.60400000000001</v>
       </c>
       <c r="F69">
-        <v>186.126</v>
+        <v>188.904</v>
       </c>
       <c r="G69">
         <v>7.55</v>
@@ -6945,28 +6945,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M69">
-        <v>16.75134</v>
+        <v>17.00136</v>
       </c>
       <c r="N69">
-        <v>11.20376204081633</v>
+        <v>10.95374204081632</v>
       </c>
       <c r="O69">
-        <v>1.120376204081633</v>
+        <v>1.095374204081632</v>
       </c>
       <c r="P69">
-        <v>10.08338583673469</v>
+        <v>9.85836783673469</v>
       </c>
       <c r="Q69">
-        <v>29.8833858367347</v>
+        <v>29.65836783673469</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1964020536536695</v>
+        <v>0.2009419065572167</v>
       </c>
       <c r="T69">
-        <v>2.329765872829691</v>
+        <v>2.399995953401326</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.66882780964486</v>
+        <v>1.644286224208906</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1193814100983093</v>
+        <v>0.1196801424909077</v>
       </c>
       <c r="C70">
-        <v>57.36716460993182</v>
+        <v>54.00763821623633</v>
       </c>
       <c r="D70">
-        <v>238.7211646099318</v>
+        <v>238.1396382162363</v>
       </c>
       <c r="E70">
-        <v>16.60400000000001</v>
+        <v>19.38200000000001</v>
       </c>
       <c r="F70">
-        <v>188.904</v>
+        <v>191.682</v>
       </c>
       <c r="G70">
         <v>7.55</v>
@@ -7027,28 +7027,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M70">
-        <v>17.00136</v>
+        <v>17.25138</v>
       </c>
       <c r="N70">
-        <v>10.95374204081632</v>
+        <v>10.70372204081632</v>
       </c>
       <c r="O70">
-        <v>1.095374204081632</v>
+        <v>1.070372204081632</v>
       </c>
       <c r="P70">
-        <v>9.85836783673469</v>
+        <v>9.633349836734691</v>
       </c>
       <c r="Q70">
-        <v>29.65836783673469</v>
+        <v>29.43334983673469</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2009419065572167</v>
+        <v>0.2057746531964765</v>
       </c>
       <c r="T70">
-        <v>2.399995953401326</v>
+        <v>2.474757006913066</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.644286224208906</v>
+        <v>1.620455989075444</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1196801424909077</v>
+        <v>0.1199788748835061</v>
       </c>
       <c r="C71">
-        <v>54.00763821623633</v>
+        <v>50.65093814217096</v>
       </c>
       <c r="D71">
-        <v>238.1396382162363</v>
+        <v>237.560938142171</v>
       </c>
       <c r="E71">
-        <v>19.38200000000001</v>
+        <v>22.16000000000003</v>
       </c>
       <c r="F71">
-        <v>191.682</v>
+        <v>194.46</v>
       </c>
       <c r="G71">
         <v>7.55</v>
@@ -7109,28 +7109,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M71">
-        <v>17.25138</v>
+        <v>17.5014</v>
       </c>
       <c r="N71">
-        <v>10.70372204081632</v>
+        <v>10.45370204081632</v>
       </c>
       <c r="O71">
-        <v>1.070372204081632</v>
+        <v>1.045370204081632</v>
       </c>
       <c r="P71">
-        <v>9.633349836734691</v>
+        <v>9.408331836734689</v>
       </c>
       <c r="Q71">
-        <v>29.43334983673469</v>
+        <v>29.20833183673469</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2057746531964765</v>
+        <v>0.2109295829450203</v>
       </c>
       <c r="T71">
-        <v>2.474757006913066</v>
+        <v>2.554502130658922</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.620455989075444</v>
+        <v>1.597306617802937</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1199788748835061</v>
+        <v>0.1202776072761045</v>
       </c>
       <c r="C72">
-        <v>50.65093814217096</v>
+        <v>47.29704383307632</v>
       </c>
       <c r="D72">
-        <v>237.560938142171</v>
+        <v>236.9850438330763</v>
       </c>
       <c r="E72">
-        <v>22.16000000000003</v>
+        <v>24.93800000000002</v>
       </c>
       <c r="F72">
-        <v>194.46</v>
+        <v>197.238</v>
       </c>
       <c r="G72">
         <v>7.55</v>
@@ -7191,28 +7191,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M72">
-        <v>17.5014</v>
+        <v>17.75142</v>
       </c>
       <c r="N72">
-        <v>10.45370204081632</v>
+        <v>10.20368204081632</v>
       </c>
       <c r="O72">
-        <v>1.045370204081632</v>
+        <v>1.020368204081632</v>
       </c>
       <c r="P72">
-        <v>9.408331836734689</v>
+        <v>9.183313836734689</v>
       </c>
       <c r="Q72">
-        <v>29.20833183673469</v>
+        <v>28.98331383673469</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2109295829450203</v>
+        <v>0.2164400250900154</v>
       </c>
       <c r="T72">
-        <v>2.554502130658922</v>
+        <v>2.639746918111389</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.597306617802937</v>
+        <v>1.574809341495853</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1202776072761045</v>
+        <v>0.1205763396687028</v>
       </c>
       <c r="C73">
-        <v>47.29704383307632</v>
+        <v>43.94593493312516</v>
       </c>
       <c r="D73">
-        <v>236.9850438330763</v>
+        <v>236.4119349331251</v>
       </c>
       <c r="E73">
-        <v>24.93799999999999</v>
+        <v>27.71599999999998</v>
       </c>
       <c r="F73">
-        <v>197.238</v>
+        <v>200.016</v>
       </c>
       <c r="G73">
         <v>7.55</v>
@@ -7273,28 +7273,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M73">
-        <v>17.75142</v>
+        <v>18.00144</v>
       </c>
       <c r="N73">
-        <v>10.20368204081633</v>
+        <v>9.953662040816326</v>
       </c>
       <c r="O73">
-        <v>1.020368204081633</v>
+        <v>0.9953662040816327</v>
       </c>
       <c r="P73">
-        <v>9.183313836734692</v>
+        <v>8.958295836734694</v>
       </c>
       <c r="Q73">
-        <v>28.98331383673469</v>
+        <v>28.7582958367347</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2164400250900154</v>
+        <v>0.2223440702453673</v>
       </c>
       <c r="T73">
-        <v>2.639746918111389</v>
+        <v>2.731080618953317</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.574809341495853</v>
+        <v>1.552936989530633</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1205763396687028</v>
+        <v>0.1208750720613012</v>
       </c>
       <c r="C74">
-        <v>43.94593493312516</v>
+        <v>40.5975912829237</v>
       </c>
       <c r="D74">
-        <v>236.4119349331251</v>
+        <v>235.8415912829237</v>
       </c>
       <c r="E74">
-        <v>27.71599999999998</v>
+        <v>30.494</v>
       </c>
       <c r="F74">
-        <v>200.016</v>
+        <v>202.794</v>
       </c>
       <c r="G74">
         <v>7.55</v>
@@ -7355,28 +7355,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M74">
-        <v>18.00144</v>
+        <v>18.25146</v>
       </c>
       <c r="N74">
-        <v>9.953662040816326</v>
+        <v>9.703642040816323</v>
       </c>
       <c r="O74">
-        <v>0.9953662040816327</v>
+        <v>0.9703642040816324</v>
       </c>
       <c r="P74">
-        <v>8.958295836734694</v>
+        <v>8.733277836734691</v>
       </c>
       <c r="Q74">
-        <v>28.7582958367347</v>
+        <v>28.53327783673469</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2223440702453673</v>
+        <v>0.2286854520788934</v>
       </c>
       <c r="T74">
-        <v>2.731080618953317</v>
+        <v>2.82917977911687</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.552936989530633</v>
+        <v>1.531663880085008</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1208750720613012</v>
+        <v>0.1211738044538996</v>
       </c>
       <c r="C75">
-        <v>40.5975912829237</v>
+        <v>37.25199291714839</v>
       </c>
       <c r="D75">
-        <v>235.8415912829237</v>
+        <v>235.2739929171484</v>
       </c>
       <c r="E75">
-        <v>30.494</v>
+        <v>33.27199999999999</v>
       </c>
       <c r="F75">
-        <v>202.794</v>
+        <v>205.572</v>
       </c>
       <c r="G75">
         <v>7.55</v>
@@ -7437,28 +7437,28 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M75">
-        <v>18.25146</v>
+        <v>18.50148</v>
       </c>
       <c r="N75">
-        <v>9.703642040816323</v>
+        <v>9.453622040816324</v>
       </c>
       <c r="O75">
-        <v>0.9703642040816324</v>
+        <v>0.9453622040816324</v>
       </c>
       <c r="P75">
-        <v>8.733277836734691</v>
+        <v>8.508259836734691</v>
       </c>
       <c r="Q75">
-        <v>28.53327783673469</v>
+        <v>28.30825983673469</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2286854520788934</v>
+        <v>0.2355146325149985</v>
       </c>
       <c r="T75">
-        <v>2.82917977911687</v>
+        <v>2.934825028523774</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.531663880085008</v>
+        <v>1.510965719543319</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1211738044538996</v>
+        <v>0.1611031205224858</v>
       </c>
       <c r="C76">
-        <v>37.25199291714839</v>
+        <v>-22.7893083428645</v>
       </c>
       <c r="D76">
-        <v>235.2739929171484</v>
+        <v>178.0106916571355</v>
       </c>
       <c r="E76">
-        <v>33.27199999999999</v>
+        <v>36.05000000000001</v>
       </c>
       <c r="F76">
-        <v>205.572</v>
+        <v>208.35</v>
       </c>
       <c r="G76">
         <v>7.55</v>
@@ -7519,45 +7519,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M76">
-        <v>18.50148</v>
+        <v>30.58578000000001</v>
       </c>
       <c r="N76">
-        <v>9.453622040816324</v>
+        <v>-2.630677959183682</v>
       </c>
       <c r="O76">
-        <v>0.9453622040816324</v>
+        <v>-0.2630677959183682</v>
       </c>
       <c r="P76">
-        <v>8.508259836734691</v>
+        <v>-2.367610163265314</v>
       </c>
       <c r="Q76">
-        <v>28.30825983673469</v>
+        <v>17.43238983673469</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2355146325149985</v>
+        <v>0.2442646088585772</v>
       </c>
       <c r="T76">
-        <v>2.934825028523774</v>
+        <v>3.070184379732993</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1</v>
+        <v>0.09139901627755226</v>
       </c>
       <c r="W76">
-        <v>0.081</v>
+        <v>0.1333826244104553</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.510965719543319</v>
+        <v>0.9139901627755225</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1611031205224858</v>
+        <v>0.1621131205224858</v>
       </c>
       <c r="C77">
-        <v>-22.7893083428645</v>
+        <v>-26.65652060823965</v>
       </c>
       <c r="D77">
-        <v>178.0106916571355</v>
+        <v>176.9214793917604</v>
       </c>
       <c r="E77">
-        <v>36.05000000000001</v>
+        <v>38.828</v>
       </c>
       <c r="F77">
-        <v>208.35</v>
+        <v>211.128</v>
       </c>
       <c r="G77">
         <v>7.55</v>
@@ -7601,37 +7601,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M77">
-        <v>30.58578000000001</v>
+        <v>30.99359040000001</v>
       </c>
       <c r="N77">
-        <v>-2.630677959183682</v>
+        <v>-3.038488359183681</v>
       </c>
       <c r="O77">
-        <v>-0.2630677959183682</v>
+        <v>-0.3038488359183681</v>
       </c>
       <c r="P77">
-        <v>-2.367610163265314</v>
+        <v>-2.734639523265313</v>
       </c>
       <c r="Q77">
-        <v>17.43238983673469</v>
+        <v>17.06536047673469</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2442646088585772</v>
+        <v>0.2525339675610179</v>
       </c>
       <c r="T77">
-        <v>3.070184379732993</v>
+        <v>3.198108728888534</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.09139901627755226</v>
+        <v>0.09019639764232129</v>
       </c>
       <c r="W77">
-        <v>0.1333826244104553</v>
+        <v>0.1335591688261072</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9139901627755225</v>
+        <v>0.9019639764232129</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1621131205224858</v>
+        <v>0.1631231205224858</v>
       </c>
       <c r="C78">
-        <v>-26.65652060823965</v>
+        <v>-30.51048458779155</v>
       </c>
       <c r="D78">
-        <v>176.9214793917604</v>
+        <v>175.8455154122084</v>
       </c>
       <c r="E78">
-        <v>38.828</v>
+        <v>41.60599999999999</v>
       </c>
       <c r="F78">
-        <v>211.128</v>
+        <v>213.906</v>
       </c>
       <c r="G78">
         <v>7.55</v>
@@ -7683,37 +7683,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M78">
-        <v>30.99359040000001</v>
+        <v>31.4014008</v>
       </c>
       <c r="N78">
-        <v>-3.038488359183681</v>
+        <v>-3.44629875918368</v>
       </c>
       <c r="O78">
-        <v>-0.3038488359183681</v>
+        <v>-0.344629875918368</v>
       </c>
       <c r="P78">
-        <v>-2.734639523265313</v>
+        <v>-3.101668883265312</v>
       </c>
       <c r="Q78">
-        <v>17.06536047673469</v>
+        <v>16.69833111673469</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2525339675610179</v>
+        <v>0.261522400933236</v>
       </c>
       <c r="T78">
-        <v>3.198108728888534</v>
+        <v>3.337156934492383</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.09019639764232129</v>
+        <v>0.08902501585475869</v>
       </c>
       <c r="W78">
-        <v>0.1335591688261072</v>
+        <v>0.1337311276725214</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9019639764232129</v>
+        <v>0.8902501585475868</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1631231205224858</v>
+        <v>0.1641331205224858</v>
       </c>
       <c r="C79">
-        <v>-30.51048458779155</v>
+        <v>-34.35144053235862</v>
       </c>
       <c r="D79">
-        <v>175.8455154122084</v>
+        <v>174.7825594676414</v>
       </c>
       <c r="E79">
-        <v>41.60599999999999</v>
+        <v>44.38400000000001</v>
       </c>
       <c r="F79">
-        <v>213.906</v>
+        <v>216.684</v>
       </c>
       <c r="G79">
         <v>7.55</v>
@@ -7765,37 +7765,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M79">
-        <v>31.4014008</v>
+        <v>31.80921120000001</v>
       </c>
       <c r="N79">
-        <v>-3.44629875918368</v>
+        <v>-3.854109159183682</v>
       </c>
       <c r="O79">
-        <v>-0.344629875918368</v>
+        <v>-0.3854109159183683</v>
       </c>
       <c r="P79">
-        <v>-3.101668883265312</v>
+        <v>-3.468698243265314</v>
       </c>
       <c r="Q79">
-        <v>16.69833111673469</v>
+        <v>16.33130175673469</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.261522400933236</v>
+        <v>0.2713279646120195</v>
       </c>
       <c r="T79">
-        <v>3.337156934492383</v>
+        <v>3.48884588606022</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.08902501585475869</v>
+        <v>0.08788366949764639</v>
       </c>
       <c r="W79">
-        <v>0.1337311276725214</v>
+        <v>0.1338986773177455</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8902501585475868</v>
+        <v>0.8788366949764639</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1641331205224858</v>
+        <v>0.1651431205224858</v>
       </c>
       <c r="C80">
-        <v>-34.35144053235862</v>
+        <v>-38.17962291858305</v>
       </c>
       <c r="D80">
-        <v>174.7825594676414</v>
+        <v>173.732377081417</v>
       </c>
       <c r="E80">
-        <v>44.38400000000001</v>
+        <v>47.16200000000001</v>
       </c>
       <c r="F80">
-        <v>216.684</v>
+        <v>219.462</v>
       </c>
       <c r="G80">
         <v>7.55</v>
@@ -7847,37 +7847,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M80">
-        <v>31.80921120000001</v>
+        <v>32.2170216</v>
       </c>
       <c r="N80">
-        <v>-3.854109159183682</v>
+        <v>-4.261919559183678</v>
       </c>
       <c r="O80">
-        <v>-0.3854109159183683</v>
+        <v>-0.4261919559183678</v>
       </c>
       <c r="P80">
-        <v>-3.468698243265314</v>
+        <v>-3.83572760326531</v>
       </c>
       <c r="Q80">
-        <v>16.33130175673469</v>
+        <v>15.96427239673469</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2713279646120195</v>
+        <v>0.2820673914983062</v>
       </c>
       <c r="T80">
-        <v>3.48884588606022</v>
+        <v>3.65498140444404</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.08788366949764639</v>
+        <v>0.08677121798501797</v>
       </c>
       <c r="W80">
-        <v>0.1338986773177455</v>
+        <v>0.1340619851997994</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8788366949764639</v>
+        <v>0.8677121798501797</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1651431205224858</v>
+        <v>0.1661531205224858</v>
       </c>
       <c r="C81">
-        <v>-38.17962291858305</v>
+        <v>-41.99526062134623</v>
       </c>
       <c r="D81">
-        <v>173.732377081417</v>
+        <v>172.6947393786538</v>
       </c>
       <c r="E81">
-        <v>47.16200000000001</v>
+        <v>49.94</v>
       </c>
       <c r="F81">
-        <v>219.462</v>
+        <v>222.24</v>
       </c>
       <c r="G81">
         <v>7.55</v>
@@ -7929,37 +7929,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M81">
-        <v>32.2170216</v>
+        <v>32.624832</v>
       </c>
       <c r="N81">
-        <v>-4.261919559183678</v>
+        <v>-4.66972995918368</v>
       </c>
       <c r="O81">
-        <v>-0.4261919559183678</v>
+        <v>-0.4669729959183681</v>
       </c>
       <c r="P81">
-        <v>-3.83572760326531</v>
+        <v>-4.202756963265312</v>
       </c>
       <c r="Q81">
-        <v>15.96427239673469</v>
+        <v>15.59724303673469</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2820673914983062</v>
+        <v>0.2938807610732215</v>
       </c>
       <c r="T81">
-        <v>3.65498140444404</v>
+        <v>3.837730474666242</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.08677121798501797</v>
+        <v>0.08568657776020523</v>
       </c>
       <c r="W81">
-        <v>0.1340619851997994</v>
+        <v>0.1342212103848019</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8677121798501797</v>
+        <v>0.8568657776020523</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1661531205224858</v>
+        <v>0.1671631205224858</v>
       </c>
       <c r="C82">
-        <v>-41.99526062134623</v>
+        <v>-45.79857708006168</v>
       </c>
       <c r="D82">
-        <v>172.6947393786538</v>
+        <v>171.6694229199383</v>
       </c>
       <c r="E82">
-        <v>49.94</v>
+        <v>52.71800000000002</v>
       </c>
       <c r="F82">
-        <v>222.24</v>
+        <v>225.018</v>
       </c>
       <c r="G82">
         <v>7.55</v>
@@ -8011,37 +8011,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M82">
-        <v>32.624832</v>
+        <v>33.03264240000001</v>
       </c>
       <c r="N82">
-        <v>-4.66972995918368</v>
+        <v>-5.077540359183683</v>
       </c>
       <c r="O82">
-        <v>-0.4669729959183681</v>
+        <v>-0.5077540359183683</v>
       </c>
       <c r="P82">
-        <v>-4.202756963265312</v>
+        <v>-4.569786323265315</v>
       </c>
       <c r="Q82">
-        <v>15.59724303673469</v>
+        <v>15.23021367673469</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2938807610732215</v>
+        <v>0.30693764323497</v>
       </c>
       <c r="T82">
-        <v>3.837730474666242</v>
+        <v>4.03971628912236</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.08568657776020523</v>
+        <v>0.08462871877551134</v>
       </c>
       <c r="W82">
-        <v>0.1342212103848019</v>
+        <v>0.134376504083755</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8568657776020523</v>
+        <v>0.8462871877551134</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1671631205224858</v>
+        <v>0.1681731205224858</v>
       </c>
       <c r="C83">
-        <v>-45.79857708006168</v>
+        <v>-49.58979045907859</v>
       </c>
       <c r="D83">
-        <v>171.6694229199383</v>
+        <v>170.6562095409214</v>
       </c>
       <c r="E83">
-        <v>52.71800000000002</v>
+        <v>55.49600000000001</v>
       </c>
       <c r="F83">
-        <v>225.018</v>
+        <v>227.796</v>
       </c>
       <c r="G83">
         <v>7.55</v>
@@ -8093,37 +8093,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M83">
-        <v>33.03264240000001</v>
+        <v>33.4404528</v>
       </c>
       <c r="N83">
-        <v>-5.077540359183683</v>
+        <v>-5.485350759183678</v>
       </c>
       <c r="O83">
-        <v>-0.5077540359183683</v>
+        <v>-0.5485350759183678</v>
       </c>
       <c r="P83">
-        <v>-4.569786323265315</v>
+        <v>-4.93681568326531</v>
       </c>
       <c r="Q83">
-        <v>15.23021367673469</v>
+        <v>14.86318431673469</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.30693764323497</v>
+        <v>0.3214452900813572</v>
       </c>
       <c r="T83">
-        <v>4.03971628912236</v>
+        <v>4.26414497185138</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.08462871877551134</v>
+        <v>0.08359666122946853</v>
       </c>
       <c r="W83">
-        <v>0.134376504083755</v>
+        <v>0.134528010131514</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8462871877551134</v>
+        <v>0.8359666122946853</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1681731205224858</v>
+        <v>0.1691831205224858</v>
       </c>
       <c r="C84">
-        <v>-49.58979045907859</v>
+        <v>-53.36911380243913</v>
       </c>
       <c r="D84">
-        <v>170.6562095409214</v>
+        <v>169.6548861975609</v>
       </c>
       <c r="E84">
-        <v>55.49600000000001</v>
+        <v>58.27400000000003</v>
       </c>
       <c r="F84">
-        <v>227.796</v>
+        <v>230.574</v>
       </c>
       <c r="G84">
         <v>7.55</v>
@@ -8175,37 +8175,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M84">
-        <v>33.4404528</v>
+        <v>33.84826320000001</v>
       </c>
       <c r="N84">
-        <v>-5.485350759183678</v>
+        <v>-5.893161159183688</v>
       </c>
       <c r="O84">
-        <v>-0.5485350759183678</v>
+        <v>-0.5893161159183687</v>
       </c>
       <c r="P84">
-        <v>-4.93681568326531</v>
+        <v>-5.303845043265319</v>
       </c>
       <c r="Q84">
-        <v>14.86318431673469</v>
+        <v>14.49615495673468</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3214452900813572</v>
+        <v>0.3376597189096724</v>
       </c>
       <c r="T84">
-        <v>4.26414497185138</v>
+        <v>4.514977029019109</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.08359666122946853</v>
+        <v>0.08258947253995684</v>
       </c>
       <c r="W84">
-        <v>0.134528010131514</v>
+        <v>0.1346758654311344</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8359666122946853</v>
+        <v>0.8258947253995683</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1691831205224858</v>
+        <v>0.1701931205224858</v>
       </c>
       <c r="C85">
-        <v>-53.36911380243913</v>
+        <v>-57.13675518321858</v>
       </c>
       <c r="D85">
-        <v>169.6548861975609</v>
+        <v>168.6652448167814</v>
       </c>
       <c r="E85">
-        <v>58.27400000000003</v>
+        <v>61.05200000000002</v>
       </c>
       <c r="F85">
-        <v>230.574</v>
+        <v>233.352</v>
       </c>
       <c r="G85">
         <v>7.55</v>
@@ -8257,37 +8257,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M85">
-        <v>33.84826320000001</v>
+        <v>34.25607360000001</v>
       </c>
       <c r="N85">
-        <v>-5.893161159183688</v>
+        <v>-6.300971559183683</v>
       </c>
       <c r="O85">
-        <v>-0.5893161159183687</v>
+        <v>-0.6300971559183683</v>
       </c>
       <c r="P85">
-        <v>-5.303845043265319</v>
+        <v>-5.670874403265315</v>
       </c>
       <c r="Q85">
-        <v>14.49615495673468</v>
+        <v>14.12912559673468</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3376597189096724</v>
+        <v>0.355900951341527</v>
       </c>
       <c r="T85">
-        <v>4.514977029019109</v>
+        <v>4.797163093332804</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.08258947253995684</v>
+        <v>0.08160626453352879</v>
       </c>
       <c r="W85">
-        <v>0.1346758654311344</v>
+        <v>0.134820200366478</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8258947253995683</v>
+        <v>0.8160626453352879</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1701931205224858</v>
+        <v>0.1712031205224858</v>
       </c>
       <c r="C86">
-        <v>-57.13675518321855</v>
+        <v>-60.89291784766931</v>
       </c>
       <c r="D86">
-        <v>168.6652448167814</v>
+        <v>167.6870821523307</v>
       </c>
       <c r="E86">
-        <v>61.05199999999999</v>
+        <v>63.82999999999998</v>
       </c>
       <c r="F86">
-        <v>233.352</v>
+        <v>236.13</v>
       </c>
       <c r="G86">
         <v>7.55</v>
@@ -8339,37 +8339,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M86">
-        <v>34.2560736</v>
+        <v>34.663884</v>
       </c>
       <c r="N86">
-        <v>-6.300971559183676</v>
+        <v>-6.708781959183678</v>
       </c>
       <c r="O86">
-        <v>-0.6300971559183677</v>
+        <v>-0.6708781959183678</v>
       </c>
       <c r="P86">
-        <v>-5.670874403265309</v>
+        <v>-6.037903763265311</v>
       </c>
       <c r="Q86">
-        <v>14.12912559673469</v>
+        <v>13.76209623673469</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3559009513415268</v>
+        <v>0.3765743480976285</v>
       </c>
       <c r="T86">
-        <v>4.7971630933328</v>
+        <v>5.116973966221654</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.08160626453352882</v>
+        <v>0.08064619083313435</v>
       </c>
       <c r="W86">
-        <v>0.134820200366478</v>
+        <v>0.1349611391856959</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8160626453352881</v>
+        <v>0.8064619083313435</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1712031205224858</v>
+        <v>0.2196350855628078</v>
       </c>
       <c r="C87">
-        <v>-60.89291784766931</v>
+        <v>-100.1574016961152</v>
       </c>
       <c r="D87">
-        <v>167.6870821523307</v>
+        <v>131.2005983038848</v>
       </c>
       <c r="E87">
-        <v>63.82999999999998</v>
+        <v>66.608</v>
       </c>
       <c r="F87">
-        <v>236.13</v>
+        <v>238.908</v>
       </c>
       <c r="G87">
         <v>7.55</v>
@@ -8421,45 +8421,45 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M87">
-        <v>34.663884</v>
+        <v>47.97272640000001</v>
       </c>
       <c r="N87">
-        <v>-6.708781959183678</v>
+        <v>-20.01762435918368</v>
       </c>
       <c r="O87">
-        <v>-0.6708781959183678</v>
+        <v>-2.001762435918368</v>
       </c>
       <c r="P87">
-        <v>-6.037903763265311</v>
+        <v>-18.01586192326531</v>
       </c>
       <c r="Q87">
-        <v>13.76209623673469</v>
+        <v>1.784138076734688</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3765743480976285</v>
+        <v>0.4072151232497592</v>
       </c>
       <c r="T87">
-        <v>5.116973966221654</v>
+        <v>5.590977012890883</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08064619083313435</v>
+        <v>0.0582729065838883</v>
       </c>
       <c r="W87">
-        <v>0.1349611391856959</v>
+        <v>0.1890988003579552</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8064619083313435</v>
+        <v>0.5827290658388831</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2196350855628078</v>
+        <v>0.2211850855628078</v>
       </c>
       <c r="C88">
-        <v>-100.1574016961152</v>
+        <v>-103.8427082947165</v>
       </c>
       <c r="D88">
-        <v>131.2005983038848</v>
+        <v>130.2932917052835</v>
       </c>
       <c r="E88">
-        <v>66.608</v>
+        <v>69.386</v>
       </c>
       <c r="F88">
-        <v>238.908</v>
+        <v>241.686</v>
       </c>
       <c r="G88">
         <v>7.55</v>
@@ -8503,37 +8503,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M88">
-        <v>47.97272640000001</v>
+        <v>48.53054880000001</v>
       </c>
       <c r="N88">
-        <v>-20.01762435918368</v>
+        <v>-20.57544675918368</v>
       </c>
       <c r="O88">
-        <v>-2.001762435918368</v>
+        <v>-2.057544675918368</v>
       </c>
       <c r="P88">
-        <v>-18.01586192326531</v>
+        <v>-18.51790208326531</v>
       </c>
       <c r="Q88">
-        <v>1.784138076734688</v>
+        <v>1.282097916734688</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4072151232497592</v>
+        <v>0.4350162865766637</v>
       </c>
       <c r="T88">
-        <v>5.590977012890883</v>
+        <v>6.021052167728643</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.0582729065838883</v>
+        <v>0.05760310305993557</v>
       </c>
       <c r="W88">
-        <v>0.1890988003579552</v>
+        <v>0.189233296905565</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5827290658388831</v>
+        <v>0.5760310305993557</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2211850855628078</v>
+        <v>0.2227350855628078</v>
       </c>
       <c r="C89">
-        <v>-103.8427082947165</v>
+        <v>-107.5155522739996</v>
       </c>
       <c r="D89">
-        <v>130.2932917052835</v>
+        <v>129.3984477260004</v>
       </c>
       <c r="E89">
-        <v>69.386</v>
+        <v>72.16399999999999</v>
       </c>
       <c r="F89">
-        <v>241.686</v>
+        <v>244.464</v>
       </c>
       <c r="G89">
         <v>7.55</v>
@@ -8585,37 +8585,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M89">
-        <v>48.53054880000001</v>
+        <v>49.0883712</v>
       </c>
       <c r="N89">
-        <v>-20.57544675918368</v>
+        <v>-21.13326915918368</v>
       </c>
       <c r="O89">
-        <v>-2.057544675918368</v>
+        <v>-2.113326915918368</v>
       </c>
       <c r="P89">
-        <v>-18.51790208326531</v>
+        <v>-19.01994224326531</v>
       </c>
       <c r="Q89">
-        <v>1.282097916734688</v>
+        <v>0.7800577567346885</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4350162865766637</v>
+        <v>0.4674509771247192</v>
       </c>
       <c r="T89">
-        <v>6.021052167728643</v>
+        <v>6.522806515039364</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.05760310305993557</v>
+        <v>0.05694852234334539</v>
       </c>
       <c r="W89">
-        <v>0.189233296905565</v>
+        <v>0.1893647367134563</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5760310305993557</v>
+        <v>0.5694852234334539</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2227350855628078</v>
+        <v>0.2242850855628078</v>
       </c>
       <c r="C90">
-        <v>-107.5155522739996</v>
+        <v>-111.1761886593097</v>
       </c>
       <c r="D90">
-        <v>129.3984477260004</v>
+        <v>128.5158113406903</v>
       </c>
       <c r="E90">
-        <v>72.16399999999999</v>
+        <v>74.94200000000001</v>
       </c>
       <c r="F90">
-        <v>244.464</v>
+        <v>247.242</v>
       </c>
       <c r="G90">
         <v>7.55</v>
@@ -8667,37 +8667,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M90">
-        <v>49.0883712</v>
+        <v>49.6461936</v>
       </c>
       <c r="N90">
-        <v>-21.13326915918368</v>
+        <v>-21.69109155918368</v>
       </c>
       <c r="O90">
-        <v>-2.113326915918368</v>
+        <v>-2.169109155918368</v>
       </c>
       <c r="P90">
-        <v>-19.01994224326531</v>
+        <v>-19.52198240326531</v>
       </c>
       <c r="Q90">
-        <v>0.7800577567346885</v>
+        <v>0.2780175967346885</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4674509771247192</v>
+        <v>0.5057828841360572</v>
       </c>
       <c r="T90">
-        <v>6.522806515039364</v>
+        <v>7.115788925497488</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.05694852234334539</v>
+        <v>0.05630865130577972</v>
       </c>
       <c r="W90">
-        <v>0.1893647367134563</v>
+        <v>0.1894932228177995</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5694852234334539</v>
+        <v>0.5630865130577971</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2242850855628078</v>
+        <v>0.2258350855628078</v>
       </c>
       <c r="C91">
-        <v>-111.1761886593097</v>
+        <v>-114.8248655649456</v>
       </c>
       <c r="D91">
-        <v>128.5158113406903</v>
+        <v>127.6451344350544</v>
       </c>
       <c r="E91">
-        <v>74.94200000000001</v>
+        <v>77.72</v>
       </c>
       <c r="F91">
-        <v>247.242</v>
+        <v>250.02</v>
       </c>
       <c r="G91">
         <v>7.55</v>
@@ -8749,37 +8749,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M91">
-        <v>49.6461936</v>
+        <v>50.204016</v>
       </c>
       <c r="N91">
-        <v>-21.69109155918368</v>
+        <v>-22.24891395918368</v>
       </c>
       <c r="O91">
-        <v>-2.169109155918368</v>
+        <v>-2.224891395918368</v>
       </c>
       <c r="P91">
-        <v>-19.52198240326531</v>
+        <v>-20.02402256326531</v>
       </c>
       <c r="Q91">
-        <v>0.2780175967346885</v>
+        <v>-0.2240225632653114</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5057828841360572</v>
+        <v>0.5517811725496629</v>
       </c>
       <c r="T91">
-        <v>7.115788925497488</v>
+        <v>7.827367818047237</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.05630865130577972</v>
+        <v>0.05568299962460438</v>
       </c>
       <c r="W91">
-        <v>0.1894932228177995</v>
+        <v>0.1896188536753794</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5630865130577971</v>
+        <v>0.5568299962460438</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2258350855628078</v>
+        <v>0.2273850855628078</v>
       </c>
       <c r="C92">
-        <v>-114.8248655649456</v>
+        <v>-118.4618244266918</v>
       </c>
       <c r="D92">
-        <v>127.6451344350544</v>
+        <v>126.7861755733082</v>
       </c>
       <c r="E92">
-        <v>77.72</v>
+        <v>80.49800000000002</v>
       </c>
       <c r="F92">
-        <v>250.02</v>
+        <v>252.798</v>
       </c>
       <c r="G92">
         <v>7.55</v>
@@ -8831,37 +8831,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M92">
-        <v>50.204016</v>
+        <v>50.76183840000001</v>
       </c>
       <c r="N92">
-        <v>-22.24891395918368</v>
+        <v>-22.80673635918368</v>
       </c>
       <c r="O92">
-        <v>-2.224891395918368</v>
+        <v>-2.280673635918368</v>
       </c>
       <c r="P92">
-        <v>-20.02402256326531</v>
+        <v>-20.52606272326532</v>
       </c>
       <c r="Q92">
-        <v>-0.2240225632653114</v>
+        <v>-0.726062723265315</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5517811725496629</v>
+        <v>0.6080013028329588</v>
       </c>
       <c r="T92">
-        <v>7.827367818047237</v>
+        <v>8.69707535338582</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.05568299962460438</v>
+        <v>0.0550710985298285</v>
       </c>
       <c r="W92">
-        <v>0.1896188536753794</v>
+        <v>0.1897417234152105</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5568299962460438</v>
+        <v>0.550710985298285</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2273850855628078</v>
+        <v>0.2289350855628078</v>
       </c>
       <c r="C93">
-        <v>-118.4618244266918</v>
+        <v>-122.0873002250235</v>
       </c>
       <c r="D93">
-        <v>126.7861755733082</v>
+        <v>125.9386997749765</v>
       </c>
       <c r="E93">
-        <v>80.49800000000002</v>
+        <v>83.27600000000001</v>
       </c>
       <c r="F93">
-        <v>252.798</v>
+        <v>255.576</v>
       </c>
       <c r="G93">
         <v>7.55</v>
@@ -8913,37 +8913,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M93">
-        <v>50.76183840000001</v>
+        <v>51.31966080000001</v>
       </c>
       <c r="N93">
-        <v>-22.80673635918368</v>
+        <v>-23.36455875918368</v>
       </c>
       <c r="O93">
-        <v>-2.280673635918368</v>
+        <v>-2.336455875918368</v>
       </c>
       <c r="P93">
-        <v>-20.52606272326532</v>
+        <v>-21.02810288326532</v>
       </c>
       <c r="Q93">
-        <v>-0.726062723265315</v>
+        <v>-1.228102883265315</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6080013028329588</v>
+        <v>0.678276465687079</v>
       </c>
       <c r="T93">
-        <v>8.69707535338582</v>
+        <v>9.784209772559052</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0550710985298285</v>
+        <v>0.05447249963276515</v>
       </c>
       <c r="W93">
-        <v>0.1897417234152105</v>
+        <v>0.1898619220737408</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.550710985298285</v>
+        <v>0.5447249963276515</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2289350855628078</v>
+        <v>0.2304850855628078</v>
       </c>
       <c r="C94">
-        <v>-122.0873002250235</v>
+        <v>-125.7015216994205</v>
       </c>
       <c r="D94">
-        <v>125.9386997749765</v>
+        <v>125.1024783005795</v>
       </c>
       <c r="E94">
-        <v>83.27600000000001</v>
+        <v>86.05400000000003</v>
       </c>
       <c r="F94">
-        <v>255.576</v>
+        <v>258.354</v>
       </c>
       <c r="G94">
         <v>7.55</v>
@@ -8995,37 +8995,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M94">
-        <v>51.31966080000001</v>
+        <v>51.87748320000001</v>
       </c>
       <c r="N94">
-        <v>-23.36455875918368</v>
+        <v>-23.92238115918368</v>
       </c>
       <c r="O94">
-        <v>-2.336455875918368</v>
+        <v>-2.392238115918369</v>
       </c>
       <c r="P94">
-        <v>-21.02810288326532</v>
+        <v>-21.53014304326532</v>
       </c>
       <c r="Q94">
-        <v>-1.228102883265315</v>
+        <v>-1.730143043265315</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.678276465687079</v>
+        <v>0.7686302464995189</v>
       </c>
       <c r="T94">
-        <v>9.784209772559052</v>
+        <v>11.18195402578177</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.05447249963276515</v>
+        <v>0.0538867738302623</v>
       </c>
       <c r="W94">
-        <v>0.1898619220737408</v>
+        <v>0.1899795358148833</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5447249963276515</v>
+        <v>0.538867738302623</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2304850855628078</v>
+        <v>0.2320350855628078</v>
       </c>
       <c r="C95">
-        <v>-125.7015216994205</v>
+        <v>-129.3047115541981</v>
       </c>
       <c r="D95">
-        <v>125.1024783005795</v>
+        <v>124.2772884458019</v>
       </c>
       <c r="E95">
-        <v>86.05400000000003</v>
+        <v>88.83199999999999</v>
       </c>
       <c r="F95">
-        <v>258.354</v>
+        <v>261.132</v>
       </c>
       <c r="G95">
         <v>7.55</v>
@@ -9077,37 +9077,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M95">
-        <v>51.87748320000001</v>
+        <v>52.4353056</v>
       </c>
       <c r="N95">
-        <v>-23.92238115918368</v>
+        <v>-24.48020355918367</v>
       </c>
       <c r="O95">
-        <v>-2.392238115918369</v>
+        <v>-2.448020355918368</v>
       </c>
       <c r="P95">
-        <v>-21.53014304326532</v>
+        <v>-22.03218320326531</v>
       </c>
       <c r="Q95">
-        <v>-1.730143043265315</v>
+        <v>-2.232183203265308</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7686302464995189</v>
+        <v>0.8891019542494389</v>
       </c>
       <c r="T95">
-        <v>11.18195402578177</v>
+        <v>13.04561303007874</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.0538867738302623</v>
+        <v>0.05331351027887654</v>
       </c>
       <c r="W95">
-        <v>0.1899795358148833</v>
+        <v>0.1900946471360016</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.538867738302623</v>
+        <v>0.5331351027887654</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2320350855628078</v>
+        <v>0.2335850855628078</v>
       </c>
       <c r="C96">
-        <v>-129.3047115541981</v>
+        <v>-132.8970866562467</v>
       </c>
       <c r="D96">
-        <v>124.2772884458019</v>
+        <v>123.4629133437533</v>
       </c>
       <c r="E96">
-        <v>88.83199999999999</v>
+        <v>91.61000000000001</v>
       </c>
       <c r="F96">
-        <v>261.132</v>
+        <v>263.91</v>
       </c>
       <c r="G96">
         <v>7.55</v>
@@ -9159,37 +9159,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M96">
-        <v>52.4353056</v>
+        <v>52.99312800000001</v>
       </c>
       <c r="N96">
-        <v>-24.48020355918367</v>
+        <v>-25.03802595918368</v>
       </c>
       <c r="O96">
-        <v>-2.448020355918368</v>
+        <v>-2.503802595918368</v>
       </c>
       <c r="P96">
-        <v>-22.03218320326531</v>
+        <v>-22.53422336326531</v>
       </c>
       <c r="Q96">
-        <v>-2.232183203265308</v>
+        <v>-2.734223363265311</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8891019542494389</v>
+        <v>1.057762345099327</v>
       </c>
       <c r="T96">
-        <v>13.04561303007874</v>
+        <v>15.65473563609449</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.05331351027887654</v>
+        <v>0.05275231543383573</v>
       </c>
       <c r="W96">
-        <v>0.1900946471360016</v>
+        <v>0.1902073350608858</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5331351027887654</v>
+        <v>0.5275231543383573</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2335850855628078</v>
+        <v>0.2351350855628078</v>
       </c>
       <c r="C97">
-        <v>-132.8970866562467</v>
+        <v>-136.4788582250457</v>
       </c>
       <c r="D97">
-        <v>123.4629133437533</v>
+        <v>122.6591417749543</v>
       </c>
       <c r="E97">
-        <v>91.61000000000001</v>
+        <v>94.38800000000003</v>
       </c>
       <c r="F97">
-        <v>263.91</v>
+        <v>266.688</v>
       </c>
       <c r="G97">
         <v>7.55</v>
@@ -9241,37 +9241,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M97">
-        <v>52.99312800000001</v>
+        <v>53.55095040000001</v>
       </c>
       <c r="N97">
-        <v>-25.03802595918368</v>
+        <v>-25.59584835918369</v>
       </c>
       <c r="O97">
-        <v>-2.503802595918368</v>
+        <v>-2.559584835918369</v>
       </c>
       <c r="P97">
-        <v>-22.53422336326531</v>
+        <v>-23.03626352326532</v>
       </c>
       <c r="Q97">
-        <v>-2.734223363265311</v>
+        <v>-3.236263523265318</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.057762345099327</v>
+        <v>1.31075293137416</v>
       </c>
       <c r="T97">
-        <v>15.65473563609449</v>
+        <v>19.56841954511813</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.05275231543383573</v>
+        <v>0.0522028121480666</v>
       </c>
       <c r="W97">
-        <v>0.1902073350608858</v>
+        <v>0.1903176753206682</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5275231543383573</v>
+        <v>0.5220281214806659</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2351350855628078</v>
+        <v>0.2366850855628078</v>
       </c>
       <c r="C98">
-        <v>-136.4788582250456</v>
+        <v>-140.0502320153046</v>
       </c>
       <c r="D98">
-        <v>122.6591417749544</v>
+        <v>121.8657679846954</v>
       </c>
       <c r="E98">
-        <v>94.38799999999998</v>
+        <v>97.166</v>
       </c>
       <c r="F98">
-        <v>266.688</v>
+        <v>269.466</v>
       </c>
       <c r="G98">
         <v>7.55</v>
@@ -9323,37 +9323,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M98">
-        <v>53.5509504</v>
+        <v>54.1087728</v>
       </c>
       <c r="N98">
-        <v>-25.59584835918367</v>
+        <v>-26.15367075918368</v>
       </c>
       <c r="O98">
-        <v>-2.559584835918367</v>
+        <v>-2.615367075918368</v>
       </c>
       <c r="P98">
-        <v>-23.0362635232653</v>
+        <v>-23.53830368326531</v>
       </c>
       <c r="Q98">
-        <v>-3.236263523265304</v>
+        <v>-3.738303683265311</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.310752931374156</v>
+        <v>1.732403908498875</v>
       </c>
       <c r="T98">
-        <v>19.56841954511807</v>
+        <v>26.09122606015744</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.05220281214806662</v>
+        <v>0.05166463882695252</v>
       </c>
       <c r="W98">
-        <v>0.1903176753206682</v>
+        <v>0.1904257405235479</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5220281214806661</v>
+        <v>0.5166463882695251</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2366850855628078</v>
+        <v>0.2382350855628078</v>
       </c>
       <c r="C99">
-        <v>-140.0502320153046</v>
+        <v>-143.6114084925613</v>
       </c>
       <c r="D99">
-        <v>121.8657679846954</v>
+        <v>121.0825915074387</v>
       </c>
       <c r="E99">
-        <v>97.166</v>
+        <v>99.94400000000002</v>
       </c>
       <c r="F99">
-        <v>269.466</v>
+        <v>272.244</v>
       </c>
       <c r="G99">
         <v>7.55</v>
@@ -9405,37 +9405,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M99">
-        <v>54.1087728</v>
+        <v>54.66659520000001</v>
       </c>
       <c r="N99">
-        <v>-26.15367075918368</v>
+        <v>-26.71149315918369</v>
       </c>
       <c r="O99">
-        <v>-2.615367075918368</v>
+        <v>-2.671149315918369</v>
       </c>
       <c r="P99">
-        <v>-23.53830368326531</v>
+        <v>-24.04034384326532</v>
       </c>
       <c r="Q99">
-        <v>-3.738303683265311</v>
+        <v>-4.240343843265318</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.732403908498875</v>
+        <v>2.575705862748312</v>
       </c>
       <c r="T99">
-        <v>26.09122606015744</v>
+        <v>39.13683909023614</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.05166463882695252</v>
+        <v>0.05113744863484076</v>
       </c>
       <c r="W99">
-        <v>0.1904257405235479</v>
+        <v>0.190531600314124</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5166463882695251</v>
+        <v>0.5113744863484075</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2382350855628078</v>
+        <v>0.2397850855628078</v>
       </c>
       <c r="C100">
-        <v>-143.6114084925613</v>
+        <v>-147.1625830020519</v>
       </c>
       <c r="D100">
-        <v>121.0825915074387</v>
+        <v>120.3094169979481</v>
       </c>
       <c r="E100">
-        <v>99.94400000000002</v>
+        <v>102.722</v>
       </c>
       <c r="F100">
-        <v>272.244</v>
+        <v>275.022</v>
       </c>
       <c r="G100">
         <v>7.55</v>
@@ -9487,37 +9487,37 @@
         <v>27.95510204081632</v>
       </c>
       <c r="M100">
-        <v>54.66659520000001</v>
+        <v>55.2244176</v>
       </c>
       <c r="N100">
-        <v>-26.71149315918369</v>
+        <v>-27.26931555918368</v>
       </c>
       <c r="O100">
-        <v>-2.671149315918369</v>
+        <v>-2.726931555918368</v>
       </c>
       <c r="P100">
-        <v>-24.04034384326532</v>
+        <v>-24.54238400326531</v>
       </c>
       <c r="Q100">
-        <v>-4.240343843265318</v>
+        <v>-4.742384003265311</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.575705862748312</v>
+        <v>5.105611725496624</v>
       </c>
       <c r="T100">
-        <v>39.13683909023614</v>
+        <v>78.27367818047229</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.05113744863484076</v>
+        <v>0.05062090874964035</v>
       </c>
       <c r="W100">
-        <v>0.190531600314124</v>
+        <v>0.1906353215230722</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5113744863484075</v>
+        <v>0.5062090874964035</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2397850855628078</v>
-      </c>
-      <c r="C101">
-        <v>-147.1625830020519</v>
-      </c>
-      <c r="D101">
-        <v>120.3094169979481</v>
-      </c>
-      <c r="E101">
-        <v>102.722</v>
-      </c>
-      <c r="F101">
-        <v>275.022</v>
-      </c>
-      <c r="G101">
-        <v>7.55</v>
-      </c>
-      <c r="H101">
-        <v>105.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>47.75510204081633</v>
-      </c>
-      <c r="K101">
-        <v>19.8</v>
-      </c>
-      <c r="L101">
-        <v>27.95510204081632</v>
-      </c>
-      <c r="M101">
-        <v>55.2244176</v>
-      </c>
-      <c r="N101">
-        <v>-27.26931555918368</v>
-      </c>
-      <c r="O101">
-        <v>-2.726931555918368</v>
-      </c>
-      <c r="P101">
-        <v>-24.54238400326531</v>
-      </c>
-      <c r="Q101">
-        <v>-4.742384003265311</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.105611725496624</v>
-      </c>
-      <c r="T101">
-        <v>78.27367818047229</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.05062090874964035</v>
-      </c>
-      <c r="W101">
-        <v>0.1906353215230722</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5062090874964035</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
